--- a/daily_schedule_template.xlsx
+++ b/daily_schedule_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://9188ucoop-my.sharepoint.com/personal/224072461_9188ucoop_onmicrosoft_com/Documents/ドキュメント/Qbrick/資料/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tente\Desktop\避難所typst\熊本大学\Qbrick\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="8_{8FAB1694-6A28-4F60-B877-78EFA3E2F1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0798F87A-2119-4E27-A64B-1B1090660AB3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB142A2-F24D-493E-BCC1-B2A59AD3C212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{B38646D7-4FB5-417F-8EB0-63EC9454F196}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B38646D7-4FB5-417F-8EB0-63EC9454F196}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,23 +23,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t>集合場所</t>
     <rPh sb="0" eb="2">
@@ -47,28 +36,6 @@
     </rPh>
     <rPh sb="2" eb="4">
       <t>バショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>支度班/俳優部出発時間</t>
-    <rPh sb="0" eb="2">
-      <t>シタク</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ハン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ハイユウ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ブ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>シュッパツ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ジカン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -332,6 +299,17 @@
     <rPh sb="6" eb="7">
       <t>ニチ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機材場所</t>
+    <rPh sb="0" eb="4">
+      <t>キザイバショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CUT</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1229,7 +1207,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1248,9 +1226,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1311,9 +1286,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1362,32 +1334,212 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1425,194 +1577,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2250,254 +2219,256 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1777715E-3AC3-4FA4-AD02-62CA73344E50}">
   <dimension ref="B1:AB41"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="3" width="12.58203125" customWidth="1"/>
-    <col min="4" max="4" width="6.58203125" customWidth="1"/>
-    <col min="5" max="7" width="12.58203125" customWidth="1"/>
-    <col min="8" max="20" width="3.58203125" customWidth="1"/>
-    <col min="21" max="21" width="21.58203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="11.83203125" customWidth="1"/>
-    <col min="24" max="24" width="21.58203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.33203125" customWidth="1"/>
-    <col min="26" max="26" width="11.9140625" customWidth="1"/>
-    <col min="27" max="28" width="9.58203125" customWidth="1"/>
+    <col min="2" max="3" width="12.59765625" customWidth="1"/>
+    <col min="4" max="4" width="6.59765625" customWidth="1"/>
+    <col min="5" max="7" width="12.59765625" customWidth="1"/>
+    <col min="8" max="20" width="3.59765625" customWidth="1"/>
+    <col min="21" max="21" width="21.59765625" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="11.796875" customWidth="1"/>
+    <col min="24" max="24" width="21.59765625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.296875" customWidth="1"/>
+    <col min="26" max="26" width="11.8984375" customWidth="1"/>
+    <col min="27" max="28" width="9.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:28" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="2" spans="2:28" ht="57.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="53" t="s">
+    <row r="1" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="2" spans="2:28" ht="57.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B2" s="111" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="112"/>
+      <c r="G2" s="112"/>
+      <c r="H2" s="112"/>
+      <c r="I2" s="112"/>
+      <c r="J2" s="112"/>
+      <c r="K2" s="112"/>
+      <c r="L2" s="112"/>
+      <c r="M2" s="112"/>
+      <c r="N2" s="112"/>
+      <c r="O2" s="112"/>
+      <c r="P2" s="112"/>
+      <c r="Q2" s="112"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="112"/>
+      <c r="T2" s="112"/>
+      <c r="U2" s="112"/>
+      <c r="V2" s="112"/>
+      <c r="W2" s="112"/>
+      <c r="X2" s="112"/>
+      <c r="Y2" s="112"/>
+      <c r="Z2" s="112"/>
+      <c r="AA2" s="112"/>
+      <c r="AB2" s="113"/>
+    </row>
+    <row r="3" spans="2:28" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B3" s="114" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54"/>
-      <c r="Q2" s="54"/>
-      <c r="R2" s="54"/>
-      <c r="S2" s="54"/>
-      <c r="T2" s="54"/>
-      <c r="U2" s="54"/>
-      <c r="V2" s="54"/>
-      <c r="W2" s="54"/>
-      <c r="X2" s="54"/>
-      <c r="Y2" s="54"/>
-      <c r="Z2" s="54"/>
-      <c r="AA2" s="54"/>
-      <c r="AB2" s="55"/>
-    </row>
-    <row r="3" spans="2:28" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="56" t="s">
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="92" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="123" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="75" t="s">
+      <c r="M3" s="123"/>
+      <c r="N3" s="123"/>
+      <c r="O3" s="123"/>
+      <c r="P3" s="123"/>
+      <c r="Q3" s="123"/>
+      <c r="R3" s="123"/>
+      <c r="S3" s="123"/>
+      <c r="T3" s="74"/>
+      <c r="U3" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="V3" s="90" t="s">
+        <v>2</v>
+      </c>
+      <c r="W3" s="75"/>
+      <c r="X3" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y3" s="74" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z3" s="75"/>
+      <c r="AA3" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB3" s="87"/>
+    </row>
+    <row r="4" spans="2:28" ht="18.45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="116"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118"/>
+      <c r="M4" s="118"/>
+      <c r="N4" s="118"/>
+      <c r="O4" s="118"/>
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118"/>
+      <c r="S4" s="118"/>
+      <c r="T4" s="119"/>
+      <c r="U4" s="120"/>
+      <c r="V4" s="91"/>
+      <c r="W4" s="80"/>
+      <c r="X4" s="121"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB4" s="43"/>
+    </row>
+    <row r="5" spans="2:28" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B5" s="116"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="118"/>
+      <c r="H5" s="118"/>
+      <c r="I5" s="118"/>
+      <c r="J5" s="118"/>
+      <c r="K5" s="118"/>
+      <c r="L5" s="118"/>
+      <c r="M5" s="118"/>
+      <c r="N5" s="118"/>
+      <c r="O5" s="118"/>
+      <c r="P5" s="118"/>
+      <c r="Q5" s="118"/>
+      <c r="R5" s="118"/>
+      <c r="S5" s="118"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="92"/>
+      <c r="W5" s="82"/>
+      <c r="X5" s="122"/>
+      <c r="Y5" s="81"/>
+      <c r="Z5" s="82"/>
+      <c r="AA5" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB5" s="45"/>
+    </row>
+    <row r="6" spans="2:28" ht="127.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="97" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="99" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="99" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="105" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="106"/>
+      <c r="G6" s="107"/>
+      <c r="H6" s="95" t="s" ph="1">
+        <v>9</v>
+      </c>
+      <c r="I6" s="103" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="103" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="101" t="s">
+        <v>11</v>
+      </c>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="39"/>
+      <c r="S6" s="40"/>
+      <c r="T6" s="40"/>
+      <c r="U6" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="V6" s="93" t="s">
+        <v>25</v>
+      </c>
+      <c r="W6" s="83" t="s">
+        <v>24</v>
+      </c>
+      <c r="X6" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
-      <c r="K3" s="76"/>
-      <c r="L3" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" s="83"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="84"/>
-      <c r="U3" s="43" t="s">
-        <v>2</v>
-      </c>
-      <c r="V3" s="87" t="s">
-        <v>3</v>
-      </c>
-      <c r="W3" s="88"/>
-      <c r="X3" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y3" s="84" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="84" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB3" s="105"/>
-    </row>
-    <row r="4" spans="2:28" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="58"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="60"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="61"/>
-      <c r="U4" s="62"/>
-      <c r="V4" s="89"/>
-      <c r="W4" s="90"/>
-      <c r="X4" s="63"/>
-      <c r="Y4" s="101"/>
-      <c r="Z4" s="90"/>
-      <c r="AA4" s="45" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB4" s="46"/>
-    </row>
-    <row r="5" spans="2:28" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="60"/>
-      <c r="L5" s="60"/>
-      <c r="M5" s="60"/>
-      <c r="N5" s="60"/>
-      <c r="O5" s="60"/>
-      <c r="P5" s="60"/>
-      <c r="Q5" s="60"/>
-      <c r="R5" s="60"/>
-      <c r="S5" s="60"/>
-      <c r="T5" s="61"/>
-      <c r="U5" s="62"/>
-      <c r="V5" s="75"/>
-      <c r="W5" s="76"/>
-      <c r="X5" s="64"/>
-      <c r="Y5" s="102"/>
-      <c r="Z5" s="76"/>
-      <c r="AA5" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB5" s="48"/>
-    </row>
-    <row r="6" spans="2:28" ht="128" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="69" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="69" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="77" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="78"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="65" t="s" ph="1">
-        <v>10</v>
-      </c>
-      <c r="I6" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="J6" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="K6" s="44"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="41"/>
-      <c r="S6" s="42"/>
-      <c r="T6" s="42"/>
-      <c r="U6" s="85" t="s">
-        <v>17</v>
-      </c>
-      <c r="V6" s="93" t="s">
-        <v>26</v>
-      </c>
-      <c r="W6" s="91" t="s">
-        <v>25</v>
-      </c>
-      <c r="X6" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="91" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z6" s="91"/>
-      <c r="AA6" s="91" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB6" s="103"/>
-    </row>
-    <row r="7" spans="2:28" ht="126.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="68"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="82"/>
-      <c r="H7" s="66" ph="1"/>
-      <c r="I7" s="74"/>
-      <c r="J7" s="72"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="50"/>
-      <c r="M7" s="51"/>
-      <c r="N7" s="51"/>
-      <c r="O7" s="51"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="50"/>
-      <c r="S7" s="50"/>
-      <c r="T7" s="52"/>
-      <c r="U7" s="86"/>
+      <c r="Y6" s="83" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z6" s="83"/>
+      <c r="AA6" s="83" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB6" s="85"/>
+    </row>
+    <row r="7" spans="2:28" ht="126.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B7" s="98"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="96" ph="1"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="104"/>
+      <c r="K7" s="102"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="47"/>
+      <c r="N7" s="47"/>
+      <c r="O7" s="47"/>
+      <c r="P7" s="47"/>
+      <c r="Q7" s="47"/>
+      <c r="R7" s="46"/>
+      <c r="S7" s="46"/>
+      <c r="T7" s="48"/>
+      <c r="U7" s="89"/>
       <c r="V7" s="94"/>
-      <c r="W7" s="92"/>
-      <c r="X7" s="92"/>
-      <c r="Y7" s="92"/>
-      <c r="Z7" s="92"/>
-      <c r="AA7" s="92"/>
-      <c r="AB7" s="104"/>
-    </row>
-    <row r="8" spans="2:28" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="13"/>
+      <c r="W7" s="84"/>
+      <c r="X7" s="84"/>
+      <c r="Y7" s="84"/>
+      <c r="Z7" s="84"/>
+      <c r="AA7" s="84"/>
+      <c r="AB7" s="86"/>
+    </row>
+    <row r="8" spans="2:28" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="12"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="13"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="12"/>
       <c r="I8" s="3"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="7"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="124"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
@@ -2506,27 +2477,27 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
-      <c r="T8" s="20"/>
-      <c r="U8" s="24"/>
-      <c r="V8" s="7"/>
+      <c r="T8" s="19"/>
+      <c r="U8" s="23"/>
+      <c r="V8" s="6"/>
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
-      <c r="AB8" s="14"/>
-    </row>
-    <row r="9" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="9"/>
+      <c r="AB8" s="13"/>
+    </row>
+    <row r="9" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B9" s="8"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="9"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="8"/>
       <c r="I9" s="1"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="5"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="31"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -2535,27 +2506,27 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="21"/>
-      <c r="U9" s="25"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="24"/>
       <c r="V9" s="5"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
       <c r="AA9" s="1"/>
-      <c r="AB9" s="10"/>
-    </row>
-    <row r="10" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="9"/>
+      <c r="AB9" s="9"/>
+    </row>
+    <row r="10" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B10" s="8"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="9"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="8"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="5"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="31"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -2564,27 +2535,27 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
-      <c r="T10" s="21"/>
-      <c r="U10" s="25"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="24"/>
       <c r="V10" s="5"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
       <c r="AA10" s="1"/>
-      <c r="AB10" s="10"/>
-    </row>
-    <row r="11" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="9"/>
+      <c r="AB10" s="9"/>
+    </row>
+    <row r="11" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B11" s="8"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="9"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="8"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="5"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="33"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -2593,27 +2564,27 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
-      <c r="T11" s="21"/>
-      <c r="U11" s="25"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="24"/>
       <c r="V11" s="5"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
       <c r="AA11" s="1"/>
-      <c r="AB11" s="10"/>
-    </row>
-    <row r="12" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="9"/>
+      <c r="AB11" s="9"/>
+    </row>
+    <row r="12" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B12" s="8"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="9"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="8"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="5"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="31"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -2622,26 +2593,26 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
-      <c r="T12" s="21"/>
-      <c r="U12" s="26"/>
-      <c r="V12" s="8"/>
+      <c r="T12" s="20"/>
+      <c r="U12" s="25"/>
+      <c r="V12" s="7"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
       <c r="AA12" s="1"/>
-      <c r="AB12" s="10"/>
-    </row>
-    <row r="13" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="9"/>
+      <c r="AB12" s="9"/>
+    </row>
+    <row r="13" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B13" s="8"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-      <c r="H13" s="9"/>
+      <c r="H13" s="8"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="5"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="31"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="O13" s="1"/>
@@ -2649,27 +2620,27 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="25"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="24"/>
       <c r="V13" s="5"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
       <c r="AA13" s="1"/>
-      <c r="AB13" s="10"/>
-    </row>
-    <row r="14" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="9"/>
+      <c r="AB13" s="9"/>
+    </row>
+    <row r="14" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B14" s="8"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="9"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="8"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="5"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="31"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
@@ -2678,27 +2649,27 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
-      <c r="T14" s="21"/>
-      <c r="U14" s="25"/>
+      <c r="T14" s="20"/>
+      <c r="U14" s="24"/>
       <c r="V14" s="5"/>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1"/>
-      <c r="AB14" s="10"/>
-    </row>
-    <row r="15" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="9"/>
+      <c r="AB14" s="9"/>
+    </row>
+    <row r="15" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B15" s="8"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="9"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="8"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="5"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="31"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -2707,27 +2678,27 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="25"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="24"/>
       <c r="V15" s="5"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1"/>
-      <c r="AB15" s="10"/>
-    </row>
-    <row r="16" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="9"/>
+      <c r="AB15" s="9"/>
+    </row>
+    <row r="16" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B16" s="8"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="9"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="8"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="5"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="31"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -2736,27 +2707,27 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
-      <c r="T16" s="21"/>
-      <c r="U16" s="25"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="24"/>
       <c r="V16" s="5"/>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
       <c r="AA16" s="1"/>
-      <c r="AB16" s="10"/>
-    </row>
-    <row r="17" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="9"/>
+      <c r="AB16" s="9"/>
+    </row>
+    <row r="17" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B17" s="8"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="9"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="8"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="5"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="31"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -2765,27 +2736,27 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
-      <c r="T17" s="21"/>
-      <c r="U17" s="25"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="24"/>
       <c r="V17" s="5"/>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
-      <c r="AB17" s="10"/>
-    </row>
-    <row r="18" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="9"/>
+      <c r="AB17" s="9"/>
+    </row>
+    <row r="18" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B18" s="8"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="9"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="8"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="5"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="31"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -2794,27 +2765,27 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
-      <c r="T18" s="21"/>
-      <c r="U18" s="25"/>
+      <c r="T18" s="20"/>
+      <c r="U18" s="24"/>
       <c r="V18" s="5"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
-      <c r="AB18" s="10"/>
-    </row>
-    <row r="19" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="9"/>
+      <c r="AB18" s="9"/>
+    </row>
+    <row r="19" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B19" s="8"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="9"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="8"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="5"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="31"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -2823,27 +2794,27 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
-      <c r="T19" s="21"/>
-      <c r="U19" s="25"/>
+      <c r="T19" s="20"/>
+      <c r="U19" s="24"/>
       <c r="V19" s="5"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
-      <c r="AB19" s="10"/>
-    </row>
-    <row r="20" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="9"/>
+      <c r="AB19" s="9"/>
+    </row>
+    <row r="20" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B20" s="8"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="9"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="8"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="5"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="31"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -2852,27 +2823,27 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
-      <c r="T20" s="21"/>
-      <c r="U20" s="25"/>
+      <c r="T20" s="20"/>
+      <c r="U20" s="24"/>
       <c r="V20" s="5"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
       <c r="AA20" s="1"/>
-      <c r="AB20" s="10"/>
-    </row>
-    <row r="21" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="9"/>
+      <c r="AB20" s="9"/>
+    </row>
+    <row r="21" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B21" s="8"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="9"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="8"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="5"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="31"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
@@ -2881,27 +2852,27 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
-      <c r="T21" s="21"/>
-      <c r="U21" s="25"/>
+      <c r="T21" s="20"/>
+      <c r="U21" s="24"/>
       <c r="V21" s="5"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
       <c r="AA21" s="1"/>
-      <c r="AB21" s="10"/>
-    </row>
-    <row r="22" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="9"/>
+      <c r="AB21" s="9"/>
+    </row>
+    <row r="22" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B22" s="8"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="9"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="8"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="5"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="31"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
@@ -2910,27 +2881,27 @@
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
-      <c r="T22" s="21"/>
-      <c r="U22" s="25"/>
-      <c r="V22" s="9"/>
+      <c r="T22" s="20"/>
+      <c r="U22" s="24"/>
+      <c r="V22" s="8"/>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
       <c r="AA22" s="1"/>
-      <c r="AB22" s="10"/>
-    </row>
-    <row r="23" spans="2:28" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B23" s="9"/>
+      <c r="AB22" s="9"/>
+    </row>
+    <row r="23" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B23" s="8"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="9"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="8"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="5"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="31"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
@@ -2939,27 +2910,27 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
-      <c r="T23" s="21"/>
-      <c r="U23" s="25"/>
-      <c r="V23" s="11"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="24"/>
+      <c r="V23" s="10"/>
       <c r="W23" s="4"/>
       <c r="X23" s="4"/>
       <c r="Y23" s="4"/>
       <c r="Z23" s="4"/>
       <c r="AA23" s="4"/>
-      <c r="AB23" s="12"/>
-    </row>
-    <row r="24" spans="2:28" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="9"/>
+      <c r="AB23" s="11"/>
+    </row>
+    <row r="24" spans="2:28" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B24" s="8"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="9"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="8"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="5"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="31"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
@@ -2968,29 +2939,29 @@
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
-      <c r="T24" s="33"/>
-      <c r="U24" s="36"/>
-      <c r="V24" s="98" t="s">
-        <v>16</v>
-      </c>
-      <c r="W24" s="99"/>
-      <c r="X24" s="99"/>
-      <c r="Y24" s="99"/>
-      <c r="Z24" s="99"/>
-      <c r="AA24" s="99"/>
-      <c r="AB24" s="100"/>
-    </row>
-    <row r="25" spans="2:28" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B25" s="9"/>
+      <c r="T24" s="31"/>
+      <c r="U24" s="34"/>
+      <c r="V24" s="76" t="s">
+        <v>15</v>
+      </c>
+      <c r="W24" s="77"/>
+      <c r="X24" s="77"/>
+      <c r="Y24" s="77"/>
+      <c r="Z24" s="77"/>
+      <c r="AA24" s="77"/>
+      <c r="AB24" s="78"/>
+    </row>
+    <row r="25" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B25" s="8"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="9"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="8"/>
       <c r="I25" s="1"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="5"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="31"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
@@ -2999,37 +2970,37 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
-      <c r="T25" s="33"/>
-      <c r="U25" s="29"/>
-      <c r="V25" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="W25" s="95" t="s">
+      <c r="T25" s="31"/>
+      <c r="U25" s="27"/>
+      <c r="V25" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="W25" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="X25" s="97"/>
-      <c r="Y25" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z25" s="39" t="s">
+      <c r="X25" s="68"/>
+      <c r="Y25" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="AA25" s="95" t="s">
+      <c r="Z25" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="AB25" s="96"/>
-    </row>
-    <row r="26" spans="2:28" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="9"/>
+      <c r="AA25" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB25" s="69"/>
+    </row>
+    <row r="26" spans="2:28" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B26" s="8"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="9"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="8"/>
       <c r="I26" s="1"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="5"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="31"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
@@ -3038,27 +3009,27 @@
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
-      <c r="T26" s="33"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="13"/>
-      <c r="W26" s="18"/>
-      <c r="X26" s="18"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="27"/>
+      <c r="V26" s="12"/>
+      <c r="W26" s="17"/>
+      <c r="X26" s="17"/>
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
-      <c r="AA26" s="18"/>
-      <c r="AB26" s="19"/>
-    </row>
-    <row r="27" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="9"/>
+      <c r="AA26" s="17"/>
+      <c r="AB26" s="18"/>
+    </row>
+    <row r="27" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B27" s="8"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="9"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="8"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="5"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="31"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
@@ -3067,27 +3038,27 @@
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
-      <c r="T27" s="33"/>
-      <c r="U27" s="29"/>
-      <c r="V27" s="9"/>
+      <c r="T27" s="31"/>
+      <c r="U27" s="27"/>
+      <c r="V27" s="8"/>
       <c r="W27" s="2"/>
       <c r="X27" s="2"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="2"/>
-      <c r="AB27" s="17"/>
-    </row>
-    <row r="28" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="9"/>
+      <c r="AB27" s="16"/>
+    </row>
+    <row r="28" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B28" s="8"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="9"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="8"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="5"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="31"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
@@ -3096,27 +3067,27 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
-      <c r="T28" s="33"/>
-      <c r="U28" s="29"/>
-      <c r="V28" s="9"/>
+      <c r="T28" s="31"/>
+      <c r="U28" s="27"/>
+      <c r="V28" s="8"/>
       <c r="W28" s="2"/>
       <c r="X28" s="2"/>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
       <c r="AA28" s="2"/>
-      <c r="AB28" s="17"/>
-    </row>
-    <row r="29" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="9"/>
+      <c r="AB28" s="16"/>
+    </row>
+    <row r="29" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B29" s="8"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="9"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="8"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="5"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="31"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
@@ -3125,27 +3096,27 @@
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
-      <c r="T29" s="33"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="9"/>
+      <c r="T29" s="31"/>
+      <c r="U29" s="27"/>
+      <c r="V29" s="8"/>
       <c r="W29" s="2"/>
       <c r="X29" s="2"/>
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
       <c r="AA29" s="2"/>
-      <c r="AB29" s="17"/>
-    </row>
-    <row r="30" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="9"/>
+      <c r="AB29" s="16"/>
+    </row>
+    <row r="30" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B30" s="8"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="9"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="8"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="5"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="31"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
@@ -3154,27 +3125,27 @@
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
-      <c r="T30" s="33"/>
-      <c r="U30" s="29"/>
-      <c r="V30" s="9"/>
+      <c r="T30" s="31"/>
+      <c r="U30" s="27"/>
+      <c r="V30" s="8"/>
       <c r="W30" s="2"/>
       <c r="X30" s="2"/>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
       <c r="AA30" s="2"/>
-      <c r="AB30" s="17"/>
-    </row>
-    <row r="31" spans="2:28" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B31" s="9"/>
+      <c r="AB30" s="16"/>
+    </row>
+    <row r="31" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B31" s="8"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="9"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="8"/>
       <c r="I31" s="1"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="5"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="31"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
@@ -3183,27 +3154,27 @@
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
-      <c r="T31" s="33"/>
-      <c r="U31" s="29"/>
-      <c r="V31" s="9"/>
+      <c r="T31" s="31"/>
+      <c r="U31" s="27"/>
+      <c r="V31" s="8"/>
       <c r="W31" s="2"/>
       <c r="X31" s="2"/>
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
       <c r="AA31" s="2"/>
-      <c r="AB31" s="17"/>
-    </row>
-    <row r="32" spans="2:28" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="9"/>
+      <c r="AB31" s="16"/>
+    </row>
+    <row r="32" spans="2:28" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B32" s="8"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="9"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="8"/>
       <c r="I32" s="1"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="5"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="31"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
@@ -3212,29 +3183,29 @@
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
-      <c r="T32" s="33"/>
-      <c r="U32" s="29"/>
-      <c r="V32" s="106" t="s">
-        <v>21</v>
-      </c>
-      <c r="W32" s="107"/>
-      <c r="X32" s="107"/>
-      <c r="Y32" s="107"/>
-      <c r="Z32" s="107"/>
-      <c r="AA32" s="107"/>
-      <c r="AB32" s="108"/>
-    </row>
-    <row r="33" spans="2:28" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B33" s="9"/>
+      <c r="T32" s="31"/>
+      <c r="U32" s="27"/>
+      <c r="V32" s="64" t="s">
+        <v>20</v>
+      </c>
+      <c r="W32" s="65"/>
+      <c r="X32" s="65"/>
+      <c r="Y32" s="65"/>
+      <c r="Z32" s="65"/>
+      <c r="AA32" s="65"/>
+      <c r="AB32" s="66"/>
+    </row>
+    <row r="33" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B33" s="8"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="9"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="8"/>
       <c r="I33" s="1"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="5"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="31"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
@@ -3243,37 +3214,37 @@
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
-      <c r="T33" s="33"/>
-      <c r="U33" s="29"/>
-      <c r="V33" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="W33" s="95" t="s">
+      <c r="T33" s="31"/>
+      <c r="U33" s="27"/>
+      <c r="V33" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="W33" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="X33" s="97"/>
-      <c r="Y33" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z33" s="39" t="s">
+      <c r="X33" s="68"/>
+      <c r="Y33" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="AA33" s="95" t="s">
+      <c r="Z33" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="AB33" s="96"/>
-    </row>
-    <row r="34" spans="2:28" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="9"/>
+      <c r="AA33" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB33" s="69"/>
+    </row>
+    <row r="34" spans="2:28" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B34" s="8"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
-      <c r="G34" s="21"/>
-      <c r="H34" s="9"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="8"/>
       <c r="I34" s="1"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="5"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="31"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
@@ -3282,85 +3253,85 @@
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
-      <c r="T34" s="33"/>
-      <c r="U34" s="29"/>
-      <c r="V34" s="9"/>
-      <c r="W34" s="122"/>
-      <c r="X34" s="123"/>
+      <c r="T34" s="31"/>
+      <c r="U34" s="27"/>
+      <c r="V34" s="8"/>
+      <c r="W34" s="58"/>
+      <c r="X34" s="59"/>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
       <c r="AA34" s="1"/>
-      <c r="AB34" s="10"/>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="9"/>
+      <c r="AB34" s="9"/>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B35" s="8"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="23"/>
-      <c r="J35" s="27"/>
-      <c r="K35" s="5"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="32"/>
       <c r="L35" s="1"/>
-      <c r="M35" s="23"/>
-      <c r="N35" s="23"/>
-      <c r="O35" s="23"/>
-      <c r="P35" s="23"/>
-      <c r="Q35" s="23"/>
+      <c r="M35" s="22"/>
+      <c r="N35" s="22"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="22"/>
+      <c r="Q35" s="22"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
-      <c r="T35" s="34"/>
-      <c r="U35" s="37"/>
-      <c r="V35" s="13"/>
-      <c r="W35" s="124"/>
-      <c r="X35" s="125"/>
+      <c r="T35" s="32"/>
+      <c r="U35" s="35"/>
+      <c r="V35" s="12"/>
+      <c r="W35" s="60"/>
+      <c r="X35" s="61"/>
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
       <c r="AA35" s="3"/>
-      <c r="AB35" s="14"/>
-    </row>
-    <row r="36" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="9"/>
+      <c r="AB35" s="13"/>
+    </row>
+    <row r="36" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B36" s="8"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="23"/>
-      <c r="J36" s="27"/>
-      <c r="K36" s="5"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="32"/>
       <c r="L36" s="1"/>
-      <c r="M36" s="23"/>
-      <c r="N36" s="23"/>
-      <c r="O36" s="23"/>
-      <c r="P36" s="23"/>
-      <c r="Q36" s="23"/>
+      <c r="M36" s="22"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="22"/>
+      <c r="P36" s="22"/>
+      <c r="Q36" s="22"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
-      <c r="T36" s="34"/>
-      <c r="U36" s="37"/>
-      <c r="V36" s="13"/>
-      <c r="W36" s="124"/>
-      <c r="X36" s="125"/>
+      <c r="T36" s="32"/>
+      <c r="U36" s="35"/>
+      <c r="V36" s="12"/>
+      <c r="W36" s="60"/>
+      <c r="X36" s="61"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
       <c r="AA36" s="3"/>
-      <c r="AB36" s="14"/>
-    </row>
-    <row r="37" spans="2:28" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B37" s="11"/>
+      <c r="AB36" s="13"/>
+    </row>
+    <row r="37" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B37" s="10"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="11"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="10"/>
       <c r="I37" s="4"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="6"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="30"/>
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
       <c r="N37" s="4"/>
@@ -3369,151 +3340,161 @@
       <c r="Q37" s="4"/>
       <c r="R37" s="4"/>
       <c r="S37" s="4"/>
-      <c r="T37" s="32"/>
-      <c r="U37" s="31"/>
-      <c r="V37" s="11"/>
-      <c r="W37" s="126"/>
-      <c r="X37" s="127"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="29"/>
+      <c r="V37" s="10"/>
+      <c r="W37" s="62"/>
+      <c r="X37" s="63"/>
       <c r="Y37" s="4"/>
       <c r="Z37" s="4"/>
       <c r="AA37" s="4"/>
-      <c r="AB37" s="12"/>
-    </row>
-    <row r="38" spans="2:28" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B38" s="109" t="s">
-        <v>28</v>
-      </c>
-      <c r="C38" s="110"/>
-      <c r="D38" s="110"/>
-      <c r="E38" s="110"/>
-      <c r="F38" s="110"/>
-      <c r="G38" s="110"/>
-      <c r="H38" s="110"/>
-      <c r="I38" s="110"/>
-      <c r="J38" s="110"/>
-      <c r="K38" s="110"/>
-      <c r="L38" s="110"/>
-      <c r="M38" s="110"/>
-      <c r="N38" s="110"/>
-      <c r="O38" s="110"/>
-      <c r="P38" s="110"/>
-      <c r="Q38" s="110"/>
-      <c r="R38" s="110"/>
-      <c r="S38" s="110"/>
-      <c r="T38" s="110"/>
-      <c r="U38" s="40" t="s">
+      <c r="AB37" s="11"/>
+    </row>
+    <row r="38" spans="2:28" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B38" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="V38" s="111" t="s">
-        <v>23</v>
-      </c>
-      <c r="W38" s="111"/>
-      <c r="X38" s="111"/>
-      <c r="Y38" s="111"/>
-      <c r="Z38" s="111"/>
-      <c r="AA38" s="111"/>
-      <c r="AB38" s="112"/>
-    </row>
-    <row r="39" spans="2:28" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="113"/>
-      <c r="C39" s="114"/>
-      <c r="D39" s="114"/>
-      <c r="E39" s="114"/>
-      <c r="F39" s="114"/>
-      <c r="G39" s="114"/>
-      <c r="H39" s="114"/>
-      <c r="I39" s="114"/>
-      <c r="J39" s="114"/>
-      <c r="K39" s="114"/>
-      <c r="L39" s="114"/>
-      <c r="M39" s="114"/>
-      <c r="N39" s="114"/>
-      <c r="O39" s="114"/>
-      <c r="P39" s="114"/>
-      <c r="Q39" s="114"/>
-      <c r="R39" s="114"/>
-      <c r="S39" s="114"/>
-      <c r="T39" s="114"/>
-      <c r="U39" s="119"/>
-      <c r="V39" s="7"/>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="71"/>
+      <c r="L38" s="71"/>
+      <c r="M38" s="71"/>
+      <c r="N38" s="71"/>
+      <c r="O38" s="71"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="71"/>
+      <c r="S38" s="71"/>
+      <c r="T38" s="71"/>
+      <c r="U38" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="V38" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="W38" s="72"/>
+      <c r="X38" s="72"/>
+      <c r="Y38" s="72"/>
+      <c r="Z38" s="72"/>
+      <c r="AA38" s="72"/>
+      <c r="AB38" s="73"/>
+    </row>
+    <row r="39" spans="2:28" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B39" s="49"/>
+      <c r="C39" s="50"/>
+      <c r="D39" s="50"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="50"/>
+      <c r="G39" s="50"/>
+      <c r="H39" s="50"/>
+      <c r="I39" s="50"/>
+      <c r="J39" s="50"/>
+      <c r="K39" s="50"/>
+      <c r="L39" s="50"/>
+      <c r="M39" s="50"/>
+      <c r="N39" s="50"/>
+      <c r="O39" s="50"/>
+      <c r="P39" s="50"/>
+      <c r="Q39" s="50"/>
+      <c r="R39" s="50"/>
+      <c r="S39" s="50"/>
+      <c r="T39" s="50"/>
+      <c r="U39" s="55"/>
+      <c r="V39" s="6"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-      <c r="AB39" s="14"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="115"/>
-      <c r="C40" s="116"/>
-      <c r="D40" s="116"/>
-      <c r="E40" s="116"/>
-      <c r="F40" s="116"/>
-      <c r="G40" s="116"/>
-      <c r="H40" s="116"/>
-      <c r="I40" s="116"/>
-      <c r="J40" s="116"/>
-      <c r="K40" s="116"/>
-      <c r="L40" s="116"/>
-      <c r="M40" s="116"/>
-      <c r="N40" s="116"/>
-      <c r="O40" s="116"/>
-      <c r="P40" s="116"/>
-      <c r="Q40" s="116"/>
-      <c r="R40" s="116"/>
-      <c r="S40" s="116"/>
-      <c r="T40" s="116"/>
-      <c r="U40" s="120"/>
-      <c r="V40" s="7"/>
+      <c r="AB39" s="13"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B40" s="51"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="52"/>
+      <c r="K40" s="52"/>
+      <c r="L40" s="52"/>
+      <c r="M40" s="52"/>
+      <c r="N40" s="52"/>
+      <c r="O40" s="52"/>
+      <c r="P40" s="52"/>
+      <c r="Q40" s="52"/>
+      <c r="R40" s="52"/>
+      <c r="S40" s="52"/>
+      <c r="T40" s="52"/>
+      <c r="U40" s="56"/>
+      <c r="V40" s="6"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-      <c r="AB40" s="14"/>
-    </row>
-    <row r="41" spans="2:28" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B41" s="117"/>
-      <c r="C41" s="118"/>
-      <c r="D41" s="118"/>
-      <c r="E41" s="118"/>
-      <c r="F41" s="118"/>
-      <c r="G41" s="118"/>
-      <c r="H41" s="118"/>
-      <c r="I41" s="118"/>
-      <c r="J41" s="118"/>
-      <c r="K41" s="118"/>
-      <c r="L41" s="118"/>
-      <c r="M41" s="118"/>
-      <c r="N41" s="118"/>
-      <c r="O41" s="118"/>
-      <c r="P41" s="118"/>
-      <c r="Q41" s="118"/>
-      <c r="R41" s="118"/>
-      <c r="S41" s="118"/>
-      <c r="T41" s="118"/>
-      <c r="U41" s="121"/>
-      <c r="V41" s="22"/>
-      <c r="W41" s="15"/>
-      <c r="X41" s="15"/>
-      <c r="Y41" s="15"/>
-      <c r="Z41" s="15"/>
-      <c r="AA41" s="15"/>
-      <c r="AB41" s="16"/>
+      <c r="AB40" s="13"/>
+    </row>
+    <row r="41" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B41" s="53"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="54"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="54"/>
+      <c r="I41" s="54"/>
+      <c r="J41" s="54"/>
+      <c r="K41" s="54"/>
+      <c r="L41" s="54"/>
+      <c r="M41" s="54"/>
+      <c r="N41" s="54"/>
+      <c r="O41" s="54"/>
+      <c r="P41" s="54"/>
+      <c r="Q41" s="54"/>
+      <c r="R41" s="54"/>
+      <c r="S41" s="54"/>
+      <c r="T41" s="54"/>
+      <c r="U41" s="57"/>
+      <c r="V41" s="21"/>
+      <c r="W41" s="14"/>
+      <c r="X41" s="14"/>
+      <c r="Y41" s="14"/>
+      <c r="Z41" s="14"/>
+      <c r="AA41" s="14"/>
+      <c r="AB41" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="B39:T41"/>
-    <mergeCell ref="U39:U41"/>
-    <mergeCell ref="W34:X34"/>
-    <mergeCell ref="W35:X35"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="W37:X37"/>
-    <mergeCell ref="V32:AB32"/>
-    <mergeCell ref="W33:X33"/>
-    <mergeCell ref="AA33:AB33"/>
-    <mergeCell ref="B38:T38"/>
-    <mergeCell ref="V38:AB38"/>
+  <mergeCells count="41">
+    <mergeCell ref="B2:AB2"/>
+    <mergeCell ref="B3:F5"/>
+    <mergeCell ref="L4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="X4:X5"/>
+    <mergeCell ref="G3:K3"/>
+    <mergeCell ref="G4:K5"/>
+    <mergeCell ref="L3:T3"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="E6:G7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="V4:W5"/>
+    <mergeCell ref="W6:W7"/>
+    <mergeCell ref="V6:V7"/>
     <mergeCell ref="AA25:AB25"/>
     <mergeCell ref="Y3:Z3"/>
     <mergeCell ref="W25:X25"/>
@@ -3523,26 +3504,17 @@
     <mergeCell ref="AA6:AB7"/>
     <mergeCell ref="X6:X7"/>
     <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="V4:W5"/>
-    <mergeCell ref="W6:W7"/>
-    <mergeCell ref="V6:V7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="E6:G7"/>
-    <mergeCell ref="B2:AB2"/>
-    <mergeCell ref="B3:F5"/>
-    <mergeCell ref="L4:T5"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="X4:X5"/>
-    <mergeCell ref="G3:K3"/>
-    <mergeCell ref="G4:K5"/>
-    <mergeCell ref="L3:T3"/>
+    <mergeCell ref="V32:AB32"/>
+    <mergeCell ref="W33:X33"/>
+    <mergeCell ref="AA33:AB33"/>
+    <mergeCell ref="B38:T38"/>
+    <mergeCell ref="V38:AB38"/>
+    <mergeCell ref="B39:T41"/>
+    <mergeCell ref="U39:U41"/>
+    <mergeCell ref="W34:X34"/>
+    <mergeCell ref="W35:X35"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="W37:X37"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/daily_schedule_template.xlsx
+++ b/daily_schedule_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tente\Desktop\避難所typst\熊本大学\Qbrick\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://9188ucoop-my.sharepoint.com/personal/224072461_9188ucoop_onmicrosoft_com/Documents/ドキュメント/Qbrick/資料/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB142A2-F24D-493E-BCC1-B2A59AD3C212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="8_{8FAB1694-6A28-4F60-B877-78EFA3E2F1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0798F87A-2119-4E27-A64B-1B1090660AB3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B38646D7-4FB5-417F-8EB0-63EC9454F196}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{B38646D7-4FB5-417F-8EB0-63EC9454F196}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,12 +23,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
     <t>集合場所</t>
     <rPh sb="0" eb="2">
@@ -36,6 +47,28 @@
     </rPh>
     <rPh sb="2" eb="4">
       <t>バショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支度班/俳優部出発時間</t>
+    <rPh sb="0" eb="2">
+      <t>シタク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ハン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハイユウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ブ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シュッパツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジカン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -299,17 +332,6 @@
     <rPh sb="6" eb="7">
       <t>ニチ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>機材場所</t>
-    <rPh sb="0" eb="4">
-      <t>キザイバショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>CUT</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1207,7 +1229,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1226,6 +1248,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1286,6 +1311,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1334,6 +1362,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1346,6 +1377,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1355,49 +1389,163 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1409,15 +1557,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1430,158 +1569,50 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2219,256 +2250,254 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1777715E-3AC3-4FA4-AD02-62CA73344E50}">
   <dimension ref="B1:AB41"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="3" width="12.59765625" customWidth="1"/>
-    <col min="4" max="4" width="6.59765625" customWidth="1"/>
-    <col min="5" max="7" width="12.59765625" customWidth="1"/>
-    <col min="8" max="20" width="3.59765625" customWidth="1"/>
-    <col min="21" max="21" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="11.796875" customWidth="1"/>
-    <col min="24" max="24" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.296875" customWidth="1"/>
-    <col min="26" max="26" width="11.8984375" customWidth="1"/>
-    <col min="27" max="28" width="9.59765625" customWidth="1"/>
+    <col min="2" max="3" width="12.58203125" customWidth="1"/>
+    <col min="4" max="4" width="6.58203125" customWidth="1"/>
+    <col min="5" max="7" width="12.58203125" customWidth="1"/>
+    <col min="8" max="20" width="3.58203125" customWidth="1"/>
+    <col min="21" max="21" width="21.58203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="11.83203125" customWidth="1"/>
+    <col min="24" max="24" width="21.58203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.33203125" customWidth="1"/>
+    <col min="26" max="26" width="11.9140625" customWidth="1"/>
+    <col min="27" max="28" width="9.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="2" spans="2:28" ht="57.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="111" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="112"/>
-      <c r="G2" s="112"/>
-      <c r="H2" s="112"/>
-      <c r="I2" s="112"/>
-      <c r="J2" s="112"/>
-      <c r="K2" s="112"/>
-      <c r="L2" s="112"/>
-      <c r="M2" s="112"/>
-      <c r="N2" s="112"/>
-      <c r="O2" s="112"/>
-      <c r="P2" s="112"/>
-      <c r="Q2" s="112"/>
-      <c r="R2" s="112"/>
-      <c r="S2" s="112"/>
-      <c r="T2" s="112"/>
-      <c r="U2" s="112"/>
-      <c r="V2" s="112"/>
-      <c r="W2" s="112"/>
-      <c r="X2" s="112"/>
-      <c r="Y2" s="112"/>
-      <c r="Z2" s="112"/>
-      <c r="AA2" s="112"/>
-      <c r="AB2" s="113"/>
-    </row>
-    <row r="3" spans="2:28" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B3" s="114" t="s">
+    <row r="1" spans="2:28" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="2" spans="2:28" ht="57.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B2" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="92" t="s">
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="54"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="54"/>
+      <c r="V2" s="54"/>
+      <c r="W2" s="54"/>
+      <c r="X2" s="54"/>
+      <c r="Y2" s="54"/>
+      <c r="Z2" s="54"/>
+      <c r="AA2" s="54"/>
+      <c r="AB2" s="55"/>
+    </row>
+    <row r="3" spans="2:28" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="56" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="92"/>
-      <c r="I3" s="92"/>
-      <c r="J3" s="92"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="123" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" s="123"/>
-      <c r="N3" s="123"/>
-      <c r="O3" s="123"/>
-      <c r="P3" s="123"/>
-      <c r="Q3" s="123"/>
-      <c r="R3" s="123"/>
-      <c r="S3" s="123"/>
-      <c r="T3" s="74"/>
-      <c r="U3" s="41" t="s">
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
+      <c r="K3" s="76"/>
+      <c r="L3" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="V3" s="90" t="s">
+      <c r="M3" s="83"/>
+      <c r="N3" s="83"/>
+      <c r="O3" s="83"/>
+      <c r="P3" s="83"/>
+      <c r="Q3" s="83"/>
+      <c r="R3" s="83"/>
+      <c r="S3" s="83"/>
+      <c r="T3" s="84"/>
+      <c r="U3" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="W3" s="75"/>
-      <c r="X3" s="39" t="s">
+      <c r="V3" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="Y3" s="74" t="s">
+      <c r="W3" s="88"/>
+      <c r="X3" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="Z3" s="75"/>
-      <c r="AA3" s="74" t="s">
+      <c r="Y3" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="AB3" s="87"/>
-    </row>
-    <row r="4" spans="2:28" ht="18.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="116"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118"/>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="118"/>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118"/>
-      <c r="S4" s="118"/>
-      <c r="T4" s="119"/>
-      <c r="U4" s="120"/>
-      <c r="V4" s="91"/>
-      <c r="W4" s="80"/>
-      <c r="X4" s="121"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="42" t="s">
+      <c r="Z3" s="88"/>
+      <c r="AA3" s="84" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB3" s="105"/>
+    </row>
+    <row r="4" spans="2:28" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="60"/>
+      <c r="N4" s="60"/>
+      <c r="O4" s="60"/>
+      <c r="P4" s="60"/>
+      <c r="Q4" s="60"/>
+      <c r="R4" s="60"/>
+      <c r="S4" s="60"/>
+      <c r="T4" s="61"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="89"/>
+      <c r="W4" s="90"/>
+      <c r="X4" s="63"/>
+      <c r="Y4" s="101"/>
+      <c r="Z4" s="90"/>
+      <c r="AA4" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB4" s="46"/>
+    </row>
+    <row r="5" spans="2:28" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="60"/>
+      <c r="L5" s="60"/>
+      <c r="M5" s="60"/>
+      <c r="N5" s="60"/>
+      <c r="O5" s="60"/>
+      <c r="P5" s="60"/>
+      <c r="Q5" s="60"/>
+      <c r="R5" s="60"/>
+      <c r="S5" s="60"/>
+      <c r="T5" s="61"/>
+      <c r="U5" s="62"/>
+      <c r="V5" s="75"/>
+      <c r="W5" s="76"/>
+      <c r="X5" s="64"/>
+      <c r="Y5" s="102"/>
+      <c r="Z5" s="76"/>
+      <c r="AA5" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB5" s="48"/>
+    </row>
+    <row r="6" spans="2:28" ht="128" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="AB4" s="43"/>
-    </row>
-    <row r="5" spans="2:28" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B5" s="116"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="118"/>
-      <c r="K5" s="118"/>
-      <c r="L5" s="118"/>
-      <c r="M5" s="118"/>
-      <c r="N5" s="118"/>
-      <c r="O5" s="118"/>
-      <c r="P5" s="118"/>
-      <c r="Q5" s="118"/>
-      <c r="R5" s="118"/>
-      <c r="S5" s="118"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="92"/>
-      <c r="W5" s="82"/>
-      <c r="X5" s="122"/>
-      <c r="Y5" s="81"/>
-      <c r="Z5" s="82"/>
-      <c r="AA5" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB5" s="45"/>
-    </row>
-    <row r="6" spans="2:28" ht="127.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="97" t="s">
+      <c r="C6" s="69" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="69" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="77" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="78"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="65" t="s" ph="1">
+        <v>10</v>
+      </c>
+      <c r="I6" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="99" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="99" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="105" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="106"/>
-      <c r="G6" s="107"/>
-      <c r="H6" s="95" t="s" ph="1">
-        <v>9</v>
-      </c>
-      <c r="I6" s="103" t="s">
-        <v>10</v>
-      </c>
-      <c r="J6" s="103" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" s="101" t="s">
-        <v>11</v>
-      </c>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="39"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="40"/>
-      <c r="U6" s="88" t="s">
-        <v>16</v>
+      <c r="K6" s="44"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="42"/>
+      <c r="T6" s="42"/>
+      <c r="U6" s="85" t="s">
+        <v>17</v>
       </c>
       <c r="V6" s="93" t="s">
+        <v>26</v>
+      </c>
+      <c r="W6" s="91" t="s">
         <v>25</v>
       </c>
-      <c r="W6" s="83" t="s">
+      <c r="X6" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="X6" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="83" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z6" s="83"/>
-      <c r="AA6" s="83" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB6" s="85"/>
-    </row>
-    <row r="7" spans="2:28" ht="126.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="98"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="109"/>
-      <c r="G7" s="110"/>
-      <c r="H7" s="96" ph="1"/>
-      <c r="I7" s="104"/>
-      <c r="J7" s="104"/>
-      <c r="K7" s="102"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="47"/>
-      <c r="N7" s="47"/>
-      <c r="O7" s="47"/>
-      <c r="P7" s="47"/>
-      <c r="Q7" s="47"/>
-      <c r="R7" s="46"/>
-      <c r="S7" s="46"/>
-      <c r="T7" s="48"/>
-      <c r="U7" s="89"/>
+      <c r="Z6" s="91"/>
+      <c r="AA6" s="91" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB6" s="103"/>
+    </row>
+    <row r="7" spans="2:28" ht="126.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="68"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="66" ph="1"/>
+      <c r="I7" s="74"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="50"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="51"/>
+      <c r="O7" s="51"/>
+      <c r="P7" s="51"/>
+      <c r="Q7" s="51"/>
+      <c r="R7" s="50"/>
+      <c r="S7" s="50"/>
+      <c r="T7" s="52"/>
+      <c r="U7" s="86"/>
       <c r="V7" s="94"/>
-      <c r="W7" s="84"/>
-      <c r="X7" s="84"/>
-      <c r="Y7" s="84"/>
-      <c r="Z7" s="84"/>
-      <c r="AA7" s="84"/>
-      <c r="AB7" s="86"/>
-    </row>
-    <row r="8" spans="2:28" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="12"/>
+      <c r="W7" s="92"/>
+      <c r="X7" s="92"/>
+      <c r="Y7" s="92"/>
+      <c r="Z7" s="92"/>
+      <c r="AA7" s="92"/>
+      <c r="AB7" s="104"/>
+    </row>
+    <row r="8" spans="2:28" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="13"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="12"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="13"/>
       <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="124"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="7"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
@@ -2477,27 +2506,27 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
-      <c r="T8" s="19"/>
-      <c r="U8" s="23"/>
-      <c r="V8" s="6"/>
+      <c r="T8" s="20"/>
+      <c r="U8" s="24"/>
+      <c r="V8" s="7"/>
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
-      <c r="AB8" s="13"/>
-    </row>
-    <row r="9" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B9" s="8"/>
+      <c r="AB8" s="14"/>
+    </row>
+    <row r="9" spans="2:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="9"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="8"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="9"/>
       <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="31"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="5"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -2506,27 +2535,27 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="20"/>
-      <c r="U9" s="24"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="25"/>
       <c r="V9" s="5"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
       <c r="AA9" s="1"/>
-      <c r="AB9" s="9"/>
-    </row>
-    <row r="10" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B10" s="8"/>
+      <c r="AB9" s="10"/>
+    </row>
+    <row r="10" spans="2:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="9"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="8"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="9"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="31"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="5"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -2535,27 +2564,27 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
-      <c r="T10" s="20"/>
-      <c r="U10" s="24"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="25"/>
       <c r="V10" s="5"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
       <c r="AA10" s="1"/>
-      <c r="AB10" s="9"/>
-    </row>
-    <row r="11" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B11" s="8"/>
+      <c r="AB10" s="10"/>
+    </row>
+    <row r="11" spans="2:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="9"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="8"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="9"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="33"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="5"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -2564,27 +2593,27 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
-      <c r="T11" s="20"/>
-      <c r="U11" s="24"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="25"/>
       <c r="V11" s="5"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
       <c r="AA11" s="1"/>
-      <c r="AB11" s="9"/>
-    </row>
-    <row r="12" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B12" s="8"/>
+      <c r="AB11" s="10"/>
+    </row>
+    <row r="12" spans="2:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="9"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="8"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="9"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="31"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="5"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -2593,26 +2622,26 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
-      <c r="T12" s="20"/>
-      <c r="U12" s="25"/>
-      <c r="V12" s="7"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="26"/>
+      <c r="V12" s="8"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
       <c r="AA12" s="1"/>
-      <c r="AB12" s="9"/>
-    </row>
-    <row r="13" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B13" s="8"/>
+      <c r="AB12" s="10"/>
+    </row>
+    <row r="13" spans="2:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="9"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-      <c r="H13" s="8"/>
+      <c r="H13" s="9"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="31"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="5"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="O13" s="1"/>
@@ -2620,27 +2649,27 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
-      <c r="T13" s="20"/>
-      <c r="U13" s="24"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="25"/>
       <c r="V13" s="5"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
       <c r="AA13" s="1"/>
-      <c r="AB13" s="9"/>
-    </row>
-    <row r="14" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B14" s="8"/>
+      <c r="AB13" s="10"/>
+    </row>
+    <row r="14" spans="2:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="9"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="8"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="9"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="31"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="5"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
@@ -2649,27 +2678,27 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
-      <c r="T14" s="20"/>
-      <c r="U14" s="24"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="25"/>
       <c r="V14" s="5"/>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1"/>
-      <c r="AB14" s="9"/>
-    </row>
-    <row r="15" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B15" s="8"/>
+      <c r="AB14" s="10"/>
+    </row>
+    <row r="15" spans="2:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="9"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="8"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="9"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="31"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="5"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -2678,27 +2707,27 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
-      <c r="T15" s="20"/>
-      <c r="U15" s="24"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="25"/>
       <c r="V15" s="5"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1"/>
-      <c r="AB15" s="9"/>
-    </row>
-    <row r="16" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B16" s="8"/>
+      <c r="AB15" s="10"/>
+    </row>
+    <row r="16" spans="2:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="9"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="8"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="9"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="31"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="5"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -2707,27 +2736,27 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
-      <c r="T16" s="20"/>
-      <c r="U16" s="24"/>
+      <c r="T16" s="21"/>
+      <c r="U16" s="25"/>
       <c r="V16" s="5"/>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
       <c r="AA16" s="1"/>
-      <c r="AB16" s="9"/>
-    </row>
-    <row r="17" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B17" s="8"/>
+      <c r="AB16" s="10"/>
+    </row>
+    <row r="17" spans="2:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="9"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="8"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="9"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="31"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="5"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -2736,27 +2765,27 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
-      <c r="T17" s="20"/>
-      <c r="U17" s="24"/>
+      <c r="T17" s="21"/>
+      <c r="U17" s="25"/>
       <c r="V17" s="5"/>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
-      <c r="AB17" s="9"/>
-    </row>
-    <row r="18" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B18" s="8"/>
+      <c r="AB17" s="10"/>
+    </row>
+    <row r="18" spans="2:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="9"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="8"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="9"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="31"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="5"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -2765,27 +2794,27 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
-      <c r="T18" s="20"/>
-      <c r="U18" s="24"/>
+      <c r="T18" s="21"/>
+      <c r="U18" s="25"/>
       <c r="V18" s="5"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
-      <c r="AB18" s="9"/>
-    </row>
-    <row r="19" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B19" s="8"/>
+      <c r="AB18" s="10"/>
+    </row>
+    <row r="19" spans="2:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="9"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="8"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="9"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="31"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="5"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -2794,27 +2823,27 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
-      <c r="T19" s="20"/>
-      <c r="U19" s="24"/>
+      <c r="T19" s="21"/>
+      <c r="U19" s="25"/>
       <c r="V19" s="5"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
-      <c r="AB19" s="9"/>
-    </row>
-    <row r="20" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B20" s="8"/>
+      <c r="AB19" s="10"/>
+    </row>
+    <row r="20" spans="2:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="9"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="8"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="9"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="31"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="5"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -2823,27 +2852,27 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
-      <c r="T20" s="20"/>
-      <c r="U20" s="24"/>
+      <c r="T20" s="21"/>
+      <c r="U20" s="25"/>
       <c r="V20" s="5"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
       <c r="AA20" s="1"/>
-      <c r="AB20" s="9"/>
-    </row>
-    <row r="21" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B21" s="8"/>
+      <c r="AB20" s="10"/>
+    </row>
+    <row r="21" spans="2:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="9"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="8"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="9"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="31"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="5"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
@@ -2852,27 +2881,27 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
-      <c r="T21" s="20"/>
-      <c r="U21" s="24"/>
+      <c r="T21" s="21"/>
+      <c r="U21" s="25"/>
       <c r="V21" s="5"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
       <c r="AA21" s="1"/>
-      <c r="AB21" s="9"/>
-    </row>
-    <row r="22" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B22" s="8"/>
+      <c r="AB21" s="10"/>
+    </row>
+    <row r="22" spans="2:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="9"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="8"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="9"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="31"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="5"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
@@ -2881,27 +2910,27 @@
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
-      <c r="T22" s="20"/>
-      <c r="U22" s="24"/>
-      <c r="V22" s="8"/>
+      <c r="T22" s="21"/>
+      <c r="U22" s="25"/>
+      <c r="V22" s="9"/>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
       <c r="AA22" s="1"/>
-      <c r="AB22" s="9"/>
-    </row>
-    <row r="23" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B23" s="8"/>
+      <c r="AB22" s="10"/>
+    </row>
+    <row r="23" spans="2:28" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B23" s="9"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="8"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="9"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="31"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="5"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
@@ -2910,27 +2939,27 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
-      <c r="T23" s="20"/>
-      <c r="U23" s="24"/>
-      <c r="V23" s="10"/>
+      <c r="T23" s="21"/>
+      <c r="U23" s="25"/>
+      <c r="V23" s="11"/>
       <c r="W23" s="4"/>
       <c r="X23" s="4"/>
       <c r="Y23" s="4"/>
       <c r="Z23" s="4"/>
       <c r="AA23" s="4"/>
-      <c r="AB23" s="11"/>
-    </row>
-    <row r="24" spans="2:28" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B24" s="8"/>
+      <c r="AB23" s="12"/>
+    </row>
+    <row r="24" spans="2:28" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="9"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="8"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="9"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="31"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="5"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
@@ -2939,29 +2968,29 @@
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
-      <c r="T24" s="31"/>
-      <c r="U24" s="34"/>
-      <c r="V24" s="76" t="s">
-        <v>15</v>
-      </c>
-      <c r="W24" s="77"/>
-      <c r="X24" s="77"/>
-      <c r="Y24" s="77"/>
-      <c r="Z24" s="77"/>
-      <c r="AA24" s="77"/>
-      <c r="AB24" s="78"/>
-    </row>
-    <row r="25" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B25" s="8"/>
+      <c r="T24" s="33"/>
+      <c r="U24" s="36"/>
+      <c r="V24" s="98" t="s">
+        <v>16</v>
+      </c>
+      <c r="W24" s="99"/>
+      <c r="X24" s="99"/>
+      <c r="Y24" s="99"/>
+      <c r="Z24" s="99"/>
+      <c r="AA24" s="99"/>
+      <c r="AB24" s="100"/>
+    </row>
+    <row r="25" spans="2:28" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B25" s="9"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="8"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="9"/>
       <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="31"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="5"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
@@ -2970,37 +2999,37 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
-      <c r="T25" s="31"/>
-      <c r="U25" s="27"/>
-      <c r="V25" s="36" t="s">
+      <c r="T25" s="33"/>
+      <c r="U25" s="29"/>
+      <c r="V25" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="W25" s="95" t="s">
+        <v>0</v>
+      </c>
+      <c r="X25" s="97"/>
+      <c r="Y25" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="W25" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="X25" s="68"/>
-      <c r="Y25" s="37" t="s">
+      <c r="Z25" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="Z25" s="37" t="s">
+      <c r="AA25" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="AA25" s="67" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB25" s="69"/>
-    </row>
-    <row r="26" spans="2:28" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B26" s="8"/>
+      <c r="AB25" s="96"/>
+    </row>
+    <row r="26" spans="2:28" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="9"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="8"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="9"/>
       <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="31"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="5"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
@@ -3009,27 +3038,27 @@
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
-      <c r="T26" s="31"/>
-      <c r="U26" s="27"/>
-      <c r="V26" s="12"/>
-      <c r="W26" s="17"/>
-      <c r="X26" s="17"/>
+      <c r="T26" s="33"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="13"/>
+      <c r="W26" s="18"/>
+      <c r="X26" s="18"/>
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
-      <c r="AA26" s="17"/>
-      <c r="AB26" s="18"/>
-    </row>
-    <row r="27" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B27" s="8"/>
+      <c r="AA26" s="18"/>
+      <c r="AB26" s="19"/>
+    </row>
+    <row r="27" spans="2:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="9"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="8"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="9"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="31"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="5"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
@@ -3038,27 +3067,27 @@
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
-      <c r="T27" s="31"/>
-      <c r="U27" s="27"/>
-      <c r="V27" s="8"/>
+      <c r="T27" s="33"/>
+      <c r="U27" s="29"/>
+      <c r="V27" s="9"/>
       <c r="W27" s="2"/>
       <c r="X27" s="2"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="2"/>
-      <c r="AB27" s="16"/>
-    </row>
-    <row r="28" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B28" s="8"/>
+      <c r="AB27" s="17"/>
+    </row>
+    <row r="28" spans="2:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="9"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="8"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="9"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="31"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="5"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
@@ -3067,27 +3096,27 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
-      <c r="T28" s="31"/>
-      <c r="U28" s="27"/>
-      <c r="V28" s="8"/>
+      <c r="T28" s="33"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="9"/>
       <c r="W28" s="2"/>
       <c r="X28" s="2"/>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
       <c r="AA28" s="2"/>
-      <c r="AB28" s="16"/>
-    </row>
-    <row r="29" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B29" s="8"/>
+      <c r="AB28" s="17"/>
+    </row>
+    <row r="29" spans="2:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="9"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="8"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="9"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="31"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="5"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
@@ -3096,27 +3125,27 @@
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
-      <c r="T29" s="31"/>
-      <c r="U29" s="27"/>
-      <c r="V29" s="8"/>
+      <c r="T29" s="33"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="9"/>
       <c r="W29" s="2"/>
       <c r="X29" s="2"/>
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
       <c r="AA29" s="2"/>
-      <c r="AB29" s="16"/>
-    </row>
-    <row r="30" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B30" s="8"/>
+      <c r="AB29" s="17"/>
+    </row>
+    <row r="30" spans="2:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="9"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="8"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="9"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="31"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="5"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
@@ -3125,27 +3154,27 @@
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
-      <c r="T30" s="31"/>
-      <c r="U30" s="27"/>
-      <c r="V30" s="8"/>
+      <c r="T30" s="33"/>
+      <c r="U30" s="29"/>
+      <c r="V30" s="9"/>
       <c r="W30" s="2"/>
       <c r="X30" s="2"/>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
       <c r="AA30" s="2"/>
-      <c r="AB30" s="16"/>
-    </row>
-    <row r="31" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="8"/>
+      <c r="AB30" s="17"/>
+    </row>
+    <row r="31" spans="2:28" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B31" s="9"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="8"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="9"/>
       <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="31"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="5"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
@@ -3154,27 +3183,27 @@
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
-      <c r="T31" s="31"/>
-      <c r="U31" s="27"/>
-      <c r="V31" s="8"/>
+      <c r="T31" s="33"/>
+      <c r="U31" s="29"/>
+      <c r="V31" s="9"/>
       <c r="W31" s="2"/>
       <c r="X31" s="2"/>
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
       <c r="AA31" s="2"/>
-      <c r="AB31" s="16"/>
-    </row>
-    <row r="32" spans="2:28" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B32" s="8"/>
+      <c r="AB31" s="17"/>
+    </row>
+    <row r="32" spans="2:28" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="9"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="8"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="9"/>
       <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="31"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="5"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
@@ -3183,29 +3212,29 @@
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
-      <c r="T32" s="31"/>
-      <c r="U32" s="27"/>
-      <c r="V32" s="64" t="s">
-        <v>20</v>
-      </c>
-      <c r="W32" s="65"/>
-      <c r="X32" s="65"/>
-      <c r="Y32" s="65"/>
-      <c r="Z32" s="65"/>
-      <c r="AA32" s="65"/>
-      <c r="AB32" s="66"/>
-    </row>
-    <row r="33" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B33" s="8"/>
+      <c r="T32" s="33"/>
+      <c r="U32" s="29"/>
+      <c r="V32" s="106" t="s">
+        <v>21</v>
+      </c>
+      <c r="W32" s="107"/>
+      <c r="X32" s="107"/>
+      <c r="Y32" s="107"/>
+      <c r="Z32" s="107"/>
+      <c r="AA32" s="107"/>
+      <c r="AB32" s="108"/>
+    </row>
+    <row r="33" spans="2:28" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B33" s="9"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="8"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="9"/>
       <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="31"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="5"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
@@ -3214,37 +3243,37 @@
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
-      <c r="T33" s="31"/>
-      <c r="U33" s="27"/>
-      <c r="V33" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="W33" s="67" t="s">
+      <c r="T33" s="33"/>
+      <c r="U33" s="29"/>
+      <c r="V33" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="W33" s="95" t="s">
         <v>0</v>
       </c>
-      <c r="X33" s="68"/>
-      <c r="Y33" s="37" t="s">
+      <c r="X33" s="97"/>
+      <c r="Y33" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z33" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="Z33" s="37" t="s">
+      <c r="AA33" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="AA33" s="67" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB33" s="69"/>
-    </row>
-    <row r="34" spans="2:28" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B34" s="8"/>
+      <c r="AB33" s="96"/>
+    </row>
+    <row r="34" spans="2:28" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" s="9"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="8"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="9"/>
       <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="31"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="5"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
@@ -3253,85 +3282,85 @@
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
-      <c r="T34" s="31"/>
-      <c r="U34" s="27"/>
-      <c r="V34" s="8"/>
-      <c r="W34" s="58"/>
-      <c r="X34" s="59"/>
+      <c r="T34" s="33"/>
+      <c r="U34" s="29"/>
+      <c r="V34" s="9"/>
+      <c r="W34" s="122"/>
+      <c r="X34" s="123"/>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
       <c r="AA34" s="1"/>
-      <c r="AB34" s="9"/>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B35" s="8"/>
+      <c r="AB34" s="10"/>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="9"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="32"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="23"/>
+      <c r="J35" s="27"/>
+      <c r="K35" s="5"/>
       <c r="L35" s="1"/>
-      <c r="M35" s="22"/>
-      <c r="N35" s="22"/>
-      <c r="O35" s="22"/>
-      <c r="P35" s="22"/>
-      <c r="Q35" s="22"/>
+      <c r="M35" s="23"/>
+      <c r="N35" s="23"/>
+      <c r="O35" s="23"/>
+      <c r="P35" s="23"/>
+      <c r="Q35" s="23"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
-      <c r="T35" s="32"/>
-      <c r="U35" s="35"/>
-      <c r="V35" s="12"/>
-      <c r="W35" s="60"/>
-      <c r="X35" s="61"/>
+      <c r="T35" s="34"/>
+      <c r="U35" s="37"/>
+      <c r="V35" s="13"/>
+      <c r="W35" s="124"/>
+      <c r="X35" s="125"/>
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
       <c r="AA35" s="3"/>
-      <c r="AB35" s="13"/>
-    </row>
-    <row r="36" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B36" s="8"/>
+      <c r="AB35" s="14"/>
+    </row>
+    <row r="36" spans="2:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" s="9"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="22"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="32"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="23"/>
+      <c r="J36" s="27"/>
+      <c r="K36" s="5"/>
       <c r="L36" s="1"/>
-      <c r="M36" s="22"/>
-      <c r="N36" s="22"/>
-      <c r="O36" s="22"/>
-      <c r="P36" s="22"/>
-      <c r="Q36" s="22"/>
+      <c r="M36" s="23"/>
+      <c r="N36" s="23"/>
+      <c r="O36" s="23"/>
+      <c r="P36" s="23"/>
+      <c r="Q36" s="23"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
-      <c r="T36" s="32"/>
-      <c r="U36" s="35"/>
-      <c r="V36" s="12"/>
-      <c r="W36" s="60"/>
-      <c r="X36" s="61"/>
+      <c r="T36" s="34"/>
+      <c r="U36" s="37"/>
+      <c r="V36" s="13"/>
+      <c r="W36" s="124"/>
+      <c r="X36" s="125"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
       <c r="AA36" s="3"/>
-      <c r="AB36" s="13"/>
-    </row>
-    <row r="37" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B37" s="10"/>
+      <c r="AB36" s="14"/>
+    </row>
+    <row r="37" spans="2:28" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B37" s="11"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="10"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="11"/>
       <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="30"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="6"/>
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
       <c r="N37" s="4"/>
@@ -3340,161 +3369,151 @@
       <c r="Q37" s="4"/>
       <c r="R37" s="4"/>
       <c r="S37" s="4"/>
-      <c r="T37" s="30"/>
-      <c r="U37" s="29"/>
-      <c r="V37" s="10"/>
-      <c r="W37" s="62"/>
-      <c r="X37" s="63"/>
+      <c r="T37" s="32"/>
+      <c r="U37" s="31"/>
+      <c r="V37" s="11"/>
+      <c r="W37" s="126"/>
+      <c r="X37" s="127"/>
       <c r="Y37" s="4"/>
       <c r="Z37" s="4"/>
       <c r="AA37" s="4"/>
-      <c r="AB37" s="11"/>
-    </row>
-    <row r="38" spans="2:28" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B38" s="70" t="s">
+      <c r="AB37" s="12"/>
+    </row>
+    <row r="38" spans="2:28" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B38" s="109" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" s="110"/>
+      <c r="D38" s="110"/>
+      <c r="E38" s="110"/>
+      <c r="F38" s="110"/>
+      <c r="G38" s="110"/>
+      <c r="H38" s="110"/>
+      <c r="I38" s="110"/>
+      <c r="J38" s="110"/>
+      <c r="K38" s="110"/>
+      <c r="L38" s="110"/>
+      <c r="M38" s="110"/>
+      <c r="N38" s="110"/>
+      <c r="O38" s="110"/>
+      <c r="P38" s="110"/>
+      <c r="Q38" s="110"/>
+      <c r="R38" s="110"/>
+      <c r="S38" s="110"/>
+      <c r="T38" s="110"/>
+      <c r="U38" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="71"/>
-      <c r="D38" s="71"/>
-      <c r="E38" s="71"/>
-      <c r="F38" s="71"/>
-      <c r="G38" s="71"/>
-      <c r="H38" s="71"/>
-      <c r="I38" s="71"/>
-      <c r="J38" s="71"/>
-      <c r="K38" s="71"/>
-      <c r="L38" s="71"/>
-      <c r="M38" s="71"/>
-      <c r="N38" s="71"/>
-      <c r="O38" s="71"/>
-      <c r="P38" s="71"/>
-      <c r="Q38" s="71"/>
-      <c r="R38" s="71"/>
-      <c r="S38" s="71"/>
-      <c r="T38" s="71"/>
-      <c r="U38" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="V38" s="72" t="s">
-        <v>22</v>
-      </c>
-      <c r="W38" s="72"/>
-      <c r="X38" s="72"/>
-      <c r="Y38" s="72"/>
-      <c r="Z38" s="72"/>
-      <c r="AA38" s="72"/>
-      <c r="AB38" s="73"/>
-    </row>
-    <row r="39" spans="2:28" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B39" s="49"/>
-      <c r="C39" s="50"/>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="50"/>
-      <c r="I39" s="50"/>
-      <c r="J39" s="50"/>
-      <c r="K39" s="50"/>
-      <c r="L39" s="50"/>
-      <c r="M39" s="50"/>
-      <c r="N39" s="50"/>
-      <c r="O39" s="50"/>
-      <c r="P39" s="50"/>
-      <c r="Q39" s="50"/>
-      <c r="R39" s="50"/>
-      <c r="S39" s="50"/>
-      <c r="T39" s="50"/>
-      <c r="U39" s="55"/>
-      <c r="V39" s="6"/>
+      <c r="V38" s="111" t="s">
+        <v>23</v>
+      </c>
+      <c r="W38" s="111"/>
+      <c r="X38" s="111"/>
+      <c r="Y38" s="111"/>
+      <c r="Z38" s="111"/>
+      <c r="AA38" s="111"/>
+      <c r="AB38" s="112"/>
+    </row>
+    <row r="39" spans="2:28" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" s="113"/>
+      <c r="C39" s="114"/>
+      <c r="D39" s="114"/>
+      <c r="E39" s="114"/>
+      <c r="F39" s="114"/>
+      <c r="G39" s="114"/>
+      <c r="H39" s="114"/>
+      <c r="I39" s="114"/>
+      <c r="J39" s="114"/>
+      <c r="K39" s="114"/>
+      <c r="L39" s="114"/>
+      <c r="M39" s="114"/>
+      <c r="N39" s="114"/>
+      <c r="O39" s="114"/>
+      <c r="P39" s="114"/>
+      <c r="Q39" s="114"/>
+      <c r="R39" s="114"/>
+      <c r="S39" s="114"/>
+      <c r="T39" s="114"/>
+      <c r="U39" s="119"/>
+      <c r="V39" s="7"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-      <c r="AB39" s="13"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B40" s="51"/>
-      <c r="C40" s="52"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="52"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="52"/>
-      <c r="K40" s="52"/>
-      <c r="L40" s="52"/>
-      <c r="M40" s="52"/>
-      <c r="N40" s="52"/>
-      <c r="O40" s="52"/>
-      <c r="P40" s="52"/>
-      <c r="Q40" s="52"/>
-      <c r="R40" s="52"/>
-      <c r="S40" s="52"/>
-      <c r="T40" s="52"/>
-      <c r="U40" s="56"/>
-      <c r="V40" s="6"/>
+      <c r="AB39" s="14"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" s="115"/>
+      <c r="C40" s="116"/>
+      <c r="D40" s="116"/>
+      <c r="E40" s="116"/>
+      <c r="F40" s="116"/>
+      <c r="G40" s="116"/>
+      <c r="H40" s="116"/>
+      <c r="I40" s="116"/>
+      <c r="J40" s="116"/>
+      <c r="K40" s="116"/>
+      <c r="L40" s="116"/>
+      <c r="M40" s="116"/>
+      <c r="N40" s="116"/>
+      <c r="O40" s="116"/>
+      <c r="P40" s="116"/>
+      <c r="Q40" s="116"/>
+      <c r="R40" s="116"/>
+      <c r="S40" s="116"/>
+      <c r="T40" s="116"/>
+      <c r="U40" s="120"/>
+      <c r="V40" s="7"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-      <c r="AB40" s="13"/>
-    </row>
-    <row r="41" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B41" s="53"/>
-      <c r="C41" s="54"/>
-      <c r="D41" s="54"/>
-      <c r="E41" s="54"/>
-      <c r="F41" s="54"/>
-      <c r="G41" s="54"/>
-      <c r="H41" s="54"/>
-      <c r="I41" s="54"/>
-      <c r="J41" s="54"/>
-      <c r="K41" s="54"/>
-      <c r="L41" s="54"/>
-      <c r="M41" s="54"/>
-      <c r="N41" s="54"/>
-      <c r="O41" s="54"/>
-      <c r="P41" s="54"/>
-      <c r="Q41" s="54"/>
-      <c r="R41" s="54"/>
-      <c r="S41" s="54"/>
-      <c r="T41" s="54"/>
-      <c r="U41" s="57"/>
-      <c r="V41" s="21"/>
-      <c r="W41" s="14"/>
-      <c r="X41" s="14"/>
-      <c r="Y41" s="14"/>
-      <c r="Z41" s="14"/>
-      <c r="AA41" s="14"/>
-      <c r="AB41" s="15"/>
+      <c r="AB40" s="14"/>
+    </row>
+    <row r="41" spans="2:28" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B41" s="117"/>
+      <c r="C41" s="118"/>
+      <c r="D41" s="118"/>
+      <c r="E41" s="118"/>
+      <c r="F41" s="118"/>
+      <c r="G41" s="118"/>
+      <c r="H41" s="118"/>
+      <c r="I41" s="118"/>
+      <c r="J41" s="118"/>
+      <c r="K41" s="118"/>
+      <c r="L41" s="118"/>
+      <c r="M41" s="118"/>
+      <c r="N41" s="118"/>
+      <c r="O41" s="118"/>
+      <c r="P41" s="118"/>
+      <c r="Q41" s="118"/>
+      <c r="R41" s="118"/>
+      <c r="S41" s="118"/>
+      <c r="T41" s="118"/>
+      <c r="U41" s="121"/>
+      <c r="V41" s="22"/>
+      <c r="W41" s="15"/>
+      <c r="X41" s="15"/>
+      <c r="Y41" s="15"/>
+      <c r="Z41" s="15"/>
+      <c r="AA41" s="15"/>
+      <c r="AB41" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="41">
-    <mergeCell ref="B2:AB2"/>
-    <mergeCell ref="B3:F5"/>
-    <mergeCell ref="L4:T5"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="X4:X5"/>
-    <mergeCell ref="G3:K3"/>
-    <mergeCell ref="G4:K5"/>
-    <mergeCell ref="L3:T3"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="E6:G7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="V4:W5"/>
-    <mergeCell ref="W6:W7"/>
-    <mergeCell ref="V6:V7"/>
+  <mergeCells count="40">
+    <mergeCell ref="B39:T41"/>
+    <mergeCell ref="U39:U41"/>
+    <mergeCell ref="W34:X34"/>
+    <mergeCell ref="W35:X35"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="W37:X37"/>
+    <mergeCell ref="V32:AB32"/>
+    <mergeCell ref="W33:X33"/>
+    <mergeCell ref="AA33:AB33"/>
+    <mergeCell ref="B38:T38"/>
+    <mergeCell ref="V38:AB38"/>
     <mergeCell ref="AA25:AB25"/>
     <mergeCell ref="Y3:Z3"/>
     <mergeCell ref="W25:X25"/>
@@ -3504,17 +3523,26 @@
     <mergeCell ref="AA6:AB7"/>
     <mergeCell ref="X6:X7"/>
     <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="V32:AB32"/>
-    <mergeCell ref="W33:X33"/>
-    <mergeCell ref="AA33:AB33"/>
-    <mergeCell ref="B38:T38"/>
-    <mergeCell ref="V38:AB38"/>
-    <mergeCell ref="B39:T41"/>
-    <mergeCell ref="U39:U41"/>
-    <mergeCell ref="W34:X34"/>
-    <mergeCell ref="W35:X35"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="W37:X37"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="V4:W5"/>
+    <mergeCell ref="W6:W7"/>
+    <mergeCell ref="V6:V7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="E6:G7"/>
+    <mergeCell ref="B2:AB2"/>
+    <mergeCell ref="B3:F5"/>
+    <mergeCell ref="L4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="X4:X5"/>
+    <mergeCell ref="G3:K3"/>
+    <mergeCell ref="G4:K5"/>
+    <mergeCell ref="L3:T3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/daily_schedule_template.xlsx
+++ b/daily_schedule_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://9188ucoop-my.sharepoint.com/personal/224072461_9188ucoop_onmicrosoft_com/Documents/ドキュメント/Qbrick/資料/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tente\Desktop\避難所HTML\Qbrick_movie_admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="8_{8FAB1694-6A28-4F60-B877-78EFA3E2F1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0798F87A-2119-4E27-A64B-1B1090660AB3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD7593B-EA95-4C50-8D36-8657D905CB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{B38646D7-4FB5-417F-8EB0-63EC9454F196}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B38646D7-4FB5-417F-8EB0-63EC9454F196}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,23 +23,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t>集合場所</t>
     <rPh sb="0" eb="2">
@@ -47,28 +36,6 @@
     </rPh>
     <rPh sb="2" eb="4">
       <t>バショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>支度班/俳優部出発時間</t>
-    <rPh sb="0" eb="2">
-      <t>シタク</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ハン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ハイユウ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ブ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>シュッパツ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ジカン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -332,6 +299,17 @@
     <rPh sb="6" eb="7">
       <t>ニチ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機材場所</t>
+    <rPh sb="0" eb="4">
+      <t>キザイバショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CUT</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1229,7 +1207,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1248,9 +1226,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1311,9 +1286,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1362,32 +1334,212 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1425,194 +1577,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2250,254 +2222,256 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1777715E-3AC3-4FA4-AD02-62CA73344E50}">
   <dimension ref="B1:AB41"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="3" width="12.58203125" customWidth="1"/>
-    <col min="4" max="4" width="6.58203125" customWidth="1"/>
-    <col min="5" max="7" width="12.58203125" customWidth="1"/>
-    <col min="8" max="20" width="3.58203125" customWidth="1"/>
-    <col min="21" max="21" width="21.58203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="11.83203125" customWidth="1"/>
-    <col min="24" max="24" width="21.58203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.33203125" customWidth="1"/>
-    <col min="26" max="26" width="11.9140625" customWidth="1"/>
-    <col min="27" max="28" width="9.58203125" customWidth="1"/>
+    <col min="2" max="3" width="12.59765625" customWidth="1"/>
+    <col min="4" max="4" width="6.59765625" customWidth="1"/>
+    <col min="5" max="7" width="12.59765625" customWidth="1"/>
+    <col min="8" max="20" width="3.59765625" customWidth="1"/>
+    <col min="21" max="21" width="21.59765625" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="11.796875" customWidth="1"/>
+    <col min="24" max="24" width="21.59765625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.296875" customWidth="1"/>
+    <col min="26" max="26" width="11.8984375" customWidth="1"/>
+    <col min="27" max="28" width="9.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:28" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="2" spans="2:28" ht="57.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="53" t="s">
+    <row r="1" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="2" spans="2:28" ht="57.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B2" s="111" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="112"/>
+      <c r="G2" s="112"/>
+      <c r="H2" s="112"/>
+      <c r="I2" s="112"/>
+      <c r="J2" s="112"/>
+      <c r="K2" s="112"/>
+      <c r="L2" s="112"/>
+      <c r="M2" s="112"/>
+      <c r="N2" s="112"/>
+      <c r="O2" s="112"/>
+      <c r="P2" s="112"/>
+      <c r="Q2" s="112"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="112"/>
+      <c r="T2" s="112"/>
+      <c r="U2" s="112"/>
+      <c r="V2" s="112"/>
+      <c r="W2" s="112"/>
+      <c r="X2" s="112"/>
+      <c r="Y2" s="112"/>
+      <c r="Z2" s="112"/>
+      <c r="AA2" s="112"/>
+      <c r="AB2" s="113"/>
+    </row>
+    <row r="3" spans="2:28" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B3" s="114" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54"/>
-      <c r="Q2" s="54"/>
-      <c r="R2" s="54"/>
-      <c r="S2" s="54"/>
-      <c r="T2" s="54"/>
-      <c r="U2" s="54"/>
-      <c r="V2" s="54"/>
-      <c r="W2" s="54"/>
-      <c r="X2" s="54"/>
-      <c r="Y2" s="54"/>
-      <c r="Z2" s="54"/>
-      <c r="AA2" s="54"/>
-      <c r="AB2" s="55"/>
-    </row>
-    <row r="3" spans="2:28" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="56" t="s">
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="92" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="123" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="75" t="s">
+      <c r="M3" s="123"/>
+      <c r="N3" s="123"/>
+      <c r="O3" s="123"/>
+      <c r="P3" s="123"/>
+      <c r="Q3" s="123"/>
+      <c r="R3" s="123"/>
+      <c r="S3" s="123"/>
+      <c r="T3" s="74"/>
+      <c r="U3" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="V3" s="90" t="s">
+        <v>2</v>
+      </c>
+      <c r="W3" s="75"/>
+      <c r="X3" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y3" s="74" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z3" s="75"/>
+      <c r="AA3" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB3" s="87"/>
+    </row>
+    <row r="4" spans="2:28" ht="18.45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="116"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118"/>
+      <c r="M4" s="118"/>
+      <c r="N4" s="118"/>
+      <c r="O4" s="118"/>
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118"/>
+      <c r="S4" s="118"/>
+      <c r="T4" s="119"/>
+      <c r="U4" s="120"/>
+      <c r="V4" s="91"/>
+      <c r="W4" s="80"/>
+      <c r="X4" s="121"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB4" s="43"/>
+    </row>
+    <row r="5" spans="2:28" ht="22.2" x14ac:dyDescent="0.45">
+      <c r="B5" s="116"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="118"/>
+      <c r="H5" s="118"/>
+      <c r="I5" s="118"/>
+      <c r="J5" s="118"/>
+      <c r="K5" s="118"/>
+      <c r="L5" s="118"/>
+      <c r="M5" s="118"/>
+      <c r="N5" s="118"/>
+      <c r="O5" s="118"/>
+      <c r="P5" s="118"/>
+      <c r="Q5" s="118"/>
+      <c r="R5" s="118"/>
+      <c r="S5" s="118"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="92"/>
+      <c r="W5" s="82"/>
+      <c r="X5" s="122"/>
+      <c r="Y5" s="81"/>
+      <c r="Z5" s="82"/>
+      <c r="AA5" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB5" s="45"/>
+    </row>
+    <row r="6" spans="2:28" ht="127.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="97" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="99" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="99" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="105" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="106"/>
+      <c r="G6" s="107"/>
+      <c r="H6" s="95" t="s" ph="1">
+        <v>9</v>
+      </c>
+      <c r="I6" s="103" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="125" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="101" t="s">
+        <v>11</v>
+      </c>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="39"/>
+      <c r="S6" s="40"/>
+      <c r="T6" s="40"/>
+      <c r="U6" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="V6" s="93" t="s">
+        <v>25</v>
+      </c>
+      <c r="W6" s="83" t="s">
+        <v>24</v>
+      </c>
+      <c r="X6" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
-      <c r="K3" s="76"/>
-      <c r="L3" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" s="83"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="84"/>
-      <c r="U3" s="43" t="s">
-        <v>2</v>
-      </c>
-      <c r="V3" s="87" t="s">
-        <v>3</v>
-      </c>
-      <c r="W3" s="88"/>
-      <c r="X3" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y3" s="84" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z3" s="88"/>
-      <c r="AA3" s="84" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB3" s="105"/>
-    </row>
-    <row r="4" spans="2:28" ht="18.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="58"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="60"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="61"/>
-      <c r="U4" s="62"/>
-      <c r="V4" s="89"/>
-      <c r="W4" s="90"/>
-      <c r="X4" s="63"/>
-      <c r="Y4" s="101"/>
-      <c r="Z4" s="90"/>
-      <c r="AA4" s="45" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB4" s="46"/>
-    </row>
-    <row r="5" spans="2:28" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="60"/>
-      <c r="L5" s="60"/>
-      <c r="M5" s="60"/>
-      <c r="N5" s="60"/>
-      <c r="O5" s="60"/>
-      <c r="P5" s="60"/>
-      <c r="Q5" s="60"/>
-      <c r="R5" s="60"/>
-      <c r="S5" s="60"/>
-      <c r="T5" s="61"/>
-      <c r="U5" s="62"/>
-      <c r="V5" s="75"/>
-      <c r="W5" s="76"/>
-      <c r="X5" s="64"/>
-      <c r="Y5" s="102"/>
-      <c r="Z5" s="76"/>
-      <c r="AA5" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB5" s="48"/>
-    </row>
-    <row r="6" spans="2:28" ht="128" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="69" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="69" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="77" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="78"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="65" t="s" ph="1">
-        <v>10</v>
-      </c>
-      <c r="I6" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="J6" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="K6" s="44"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="41"/>
-      <c r="S6" s="42"/>
-      <c r="T6" s="42"/>
-      <c r="U6" s="85" t="s">
-        <v>17</v>
-      </c>
-      <c r="V6" s="93" t="s">
-        <v>26</v>
-      </c>
-      <c r="W6" s="91" t="s">
-        <v>25</v>
-      </c>
-      <c r="X6" s="91" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="91" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z6" s="91"/>
-      <c r="AA6" s="91" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB6" s="103"/>
-    </row>
-    <row r="7" spans="2:28" ht="126.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="68"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="82"/>
-      <c r="H7" s="66" ph="1"/>
-      <c r="I7" s="74"/>
-      <c r="J7" s="72"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="50"/>
-      <c r="M7" s="51"/>
-      <c r="N7" s="51"/>
-      <c r="O7" s="51"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="50"/>
-      <c r="S7" s="50"/>
-      <c r="T7" s="52"/>
-      <c r="U7" s="86"/>
+      <c r="Y6" s="83" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z6" s="83"/>
+      <c r="AA6" s="83" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB6" s="85"/>
+    </row>
+    <row r="7" spans="2:28" ht="126.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B7" s="98"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="96" ph="1"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="104"/>
+      <c r="K7" s="102"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="47"/>
+      <c r="N7" s="47"/>
+      <c r="O7" s="47"/>
+      <c r="P7" s="47"/>
+      <c r="Q7" s="47"/>
+      <c r="R7" s="46"/>
+      <c r="S7" s="46"/>
+      <c r="T7" s="48"/>
+      <c r="U7" s="89"/>
       <c r="V7" s="94"/>
-      <c r="W7" s="92"/>
-      <c r="X7" s="92"/>
-      <c r="Y7" s="92"/>
-      <c r="Z7" s="92"/>
-      <c r="AA7" s="92"/>
-      <c r="AB7" s="104"/>
-    </row>
-    <row r="8" spans="2:28" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="13"/>
+      <c r="W7" s="84"/>
+      <c r="X7" s="84"/>
+      <c r="Y7" s="84"/>
+      <c r="Z7" s="84"/>
+      <c r="AA7" s="84"/>
+      <c r="AB7" s="86"/>
+    </row>
+    <row r="8" spans="2:28" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="12"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="13"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="12"/>
       <c r="I8" s="3"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="7"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="124"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
@@ -2506,27 +2480,27 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
-      <c r="T8" s="20"/>
-      <c r="U8" s="24"/>
-      <c r="V8" s="7"/>
+      <c r="T8" s="19"/>
+      <c r="U8" s="23"/>
+      <c r="V8" s="6"/>
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
-      <c r="AB8" s="14"/>
-    </row>
-    <row r="9" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="9"/>
+      <c r="AB8" s="13"/>
+    </row>
+    <row r="9" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B9" s="8"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="9"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="8"/>
       <c r="I9" s="1"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="5"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="31"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -2535,27 +2509,27 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="21"/>
-      <c r="U9" s="25"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="24"/>
       <c r="V9" s="5"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
       <c r="AA9" s="1"/>
-      <c r="AB9" s="10"/>
-    </row>
-    <row r="10" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="9"/>
+      <c r="AB9" s="9"/>
+    </row>
+    <row r="10" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B10" s="8"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="9"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="8"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="5"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="31"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -2564,27 +2538,27 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
-      <c r="T10" s="21"/>
-      <c r="U10" s="25"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="24"/>
       <c r="V10" s="5"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
       <c r="AA10" s="1"/>
-      <c r="AB10" s="10"/>
-    </row>
-    <row r="11" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="9"/>
+      <c r="AB10" s="9"/>
+    </row>
+    <row r="11" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B11" s="8"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="9"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="8"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="5"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="33"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -2593,27 +2567,27 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
-      <c r="T11" s="21"/>
-      <c r="U11" s="25"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="24"/>
       <c r="V11" s="5"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
       <c r="AA11" s="1"/>
-      <c r="AB11" s="10"/>
-    </row>
-    <row r="12" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="9"/>
+      <c r="AB11" s="9"/>
+    </row>
+    <row r="12" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B12" s="8"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="9"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="8"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="5"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="31"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -2622,26 +2596,26 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
-      <c r="T12" s="21"/>
-      <c r="U12" s="26"/>
-      <c r="V12" s="8"/>
+      <c r="T12" s="20"/>
+      <c r="U12" s="25"/>
+      <c r="V12" s="7"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
       <c r="AA12" s="1"/>
-      <c r="AB12" s="10"/>
-    </row>
-    <row r="13" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="9"/>
+      <c r="AB12" s="9"/>
+    </row>
+    <row r="13" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B13" s="8"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-      <c r="H13" s="9"/>
+      <c r="H13" s="8"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="5"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="31"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="O13" s="1"/>
@@ -2649,27 +2623,27 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="25"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="24"/>
       <c r="V13" s="5"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
       <c r="AA13" s="1"/>
-      <c r="AB13" s="10"/>
-    </row>
-    <row r="14" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="9"/>
+      <c r="AB13" s="9"/>
+    </row>
+    <row r="14" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B14" s="8"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="9"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="8"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="5"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="31"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
@@ -2678,27 +2652,27 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
-      <c r="T14" s="21"/>
-      <c r="U14" s="25"/>
+      <c r="T14" s="20"/>
+      <c r="U14" s="24"/>
       <c r="V14" s="5"/>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1"/>
-      <c r="AB14" s="10"/>
-    </row>
-    <row r="15" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="9"/>
+      <c r="AB14" s="9"/>
+    </row>
+    <row r="15" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B15" s="8"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="9"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="8"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="5"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="31"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -2707,27 +2681,27 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="25"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="24"/>
       <c r="V15" s="5"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1"/>
-      <c r="AB15" s="10"/>
-    </row>
-    <row r="16" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="9"/>
+      <c r="AB15" s="9"/>
+    </row>
+    <row r="16" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B16" s="8"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="9"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="8"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="5"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="31"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -2736,27 +2710,27 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
-      <c r="T16" s="21"/>
-      <c r="U16" s="25"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="24"/>
       <c r="V16" s="5"/>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
       <c r="AA16" s="1"/>
-      <c r="AB16" s="10"/>
-    </row>
-    <row r="17" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="9"/>
+      <c r="AB16" s="9"/>
+    </row>
+    <row r="17" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B17" s="8"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="9"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="8"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="5"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="31"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -2765,27 +2739,27 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
-      <c r="T17" s="21"/>
-      <c r="U17" s="25"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="24"/>
       <c r="V17" s="5"/>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
-      <c r="AB17" s="10"/>
-    </row>
-    <row r="18" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="9"/>
+      <c r="AB17" s="9"/>
+    </row>
+    <row r="18" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B18" s="8"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="9"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="8"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="5"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="31"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -2794,27 +2768,27 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
-      <c r="T18" s="21"/>
-      <c r="U18" s="25"/>
+      <c r="T18" s="20"/>
+      <c r="U18" s="24"/>
       <c r="V18" s="5"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
-      <c r="AB18" s="10"/>
-    </row>
-    <row r="19" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="9"/>
+      <c r="AB18" s="9"/>
+    </row>
+    <row r="19" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B19" s="8"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="9"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="8"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="5"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="31"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -2823,27 +2797,27 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
-      <c r="T19" s="21"/>
-      <c r="U19" s="25"/>
+      <c r="T19" s="20"/>
+      <c r="U19" s="24"/>
       <c r="V19" s="5"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
-      <c r="AB19" s="10"/>
-    </row>
-    <row r="20" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="9"/>
+      <c r="AB19" s="9"/>
+    </row>
+    <row r="20" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B20" s="8"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="9"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="8"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="5"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="31"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -2852,27 +2826,27 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
-      <c r="T20" s="21"/>
-      <c r="U20" s="25"/>
+      <c r="T20" s="20"/>
+      <c r="U20" s="24"/>
       <c r="V20" s="5"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
       <c r="AA20" s="1"/>
-      <c r="AB20" s="10"/>
-    </row>
-    <row r="21" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="9"/>
+      <c r="AB20" s="9"/>
+    </row>
+    <row r="21" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B21" s="8"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="9"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="8"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="5"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="31"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
@@ -2881,27 +2855,27 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
-      <c r="T21" s="21"/>
-      <c r="U21" s="25"/>
+      <c r="T21" s="20"/>
+      <c r="U21" s="24"/>
       <c r="V21" s="5"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
       <c r="AA21" s="1"/>
-      <c r="AB21" s="10"/>
-    </row>
-    <row r="22" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="9"/>
+      <c r="AB21" s="9"/>
+    </row>
+    <row r="22" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B22" s="8"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="9"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="8"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="5"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="31"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
@@ -2910,27 +2884,27 @@
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
-      <c r="T22" s="21"/>
-      <c r="U22" s="25"/>
-      <c r="V22" s="9"/>
+      <c r="T22" s="20"/>
+      <c r="U22" s="24"/>
+      <c r="V22" s="8"/>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
       <c r="AA22" s="1"/>
-      <c r="AB22" s="10"/>
-    </row>
-    <row r="23" spans="2:28" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B23" s="9"/>
+      <c r="AB22" s="9"/>
+    </row>
+    <row r="23" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B23" s="8"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="9"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="8"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="5"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="31"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
@@ -2939,27 +2913,27 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
-      <c r="T23" s="21"/>
-      <c r="U23" s="25"/>
-      <c r="V23" s="11"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="24"/>
+      <c r="V23" s="10"/>
       <c r="W23" s="4"/>
       <c r="X23" s="4"/>
       <c r="Y23" s="4"/>
       <c r="Z23" s="4"/>
       <c r="AA23" s="4"/>
-      <c r="AB23" s="12"/>
-    </row>
-    <row r="24" spans="2:28" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="9"/>
+      <c r="AB23" s="11"/>
+    </row>
+    <row r="24" spans="2:28" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B24" s="8"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="9"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="8"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="5"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="31"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
@@ -2968,29 +2942,29 @@
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
-      <c r="T24" s="33"/>
-      <c r="U24" s="36"/>
-      <c r="V24" s="98" t="s">
-        <v>16</v>
-      </c>
-      <c r="W24" s="99"/>
-      <c r="X24" s="99"/>
-      <c r="Y24" s="99"/>
-      <c r="Z24" s="99"/>
-      <c r="AA24" s="99"/>
-      <c r="AB24" s="100"/>
-    </row>
-    <row r="25" spans="2:28" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B25" s="9"/>
+      <c r="T24" s="31"/>
+      <c r="U24" s="34"/>
+      <c r="V24" s="76" t="s">
+        <v>15</v>
+      </c>
+      <c r="W24" s="77"/>
+      <c r="X24" s="77"/>
+      <c r="Y24" s="77"/>
+      <c r="Z24" s="77"/>
+      <c r="AA24" s="77"/>
+      <c r="AB24" s="78"/>
+    </row>
+    <row r="25" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B25" s="8"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="9"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="8"/>
       <c r="I25" s="1"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="5"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="31"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
@@ -2999,37 +2973,37 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
-      <c r="T25" s="33"/>
-      <c r="U25" s="29"/>
-      <c r="V25" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="W25" s="95" t="s">
+      <c r="T25" s="31"/>
+      <c r="U25" s="27"/>
+      <c r="V25" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="W25" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="X25" s="97"/>
-      <c r="Y25" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z25" s="39" t="s">
+      <c r="X25" s="68"/>
+      <c r="Y25" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="AA25" s="95" t="s">
+      <c r="Z25" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="AB25" s="96"/>
-    </row>
-    <row r="26" spans="2:28" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="9"/>
+      <c r="AA25" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB25" s="69"/>
+    </row>
+    <row r="26" spans="2:28" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B26" s="8"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="9"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="8"/>
       <c r="I26" s="1"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="5"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="31"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
@@ -3038,27 +3012,27 @@
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
-      <c r="T26" s="33"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="13"/>
-      <c r="W26" s="18"/>
-      <c r="X26" s="18"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="27"/>
+      <c r="V26" s="12"/>
+      <c r="W26" s="17"/>
+      <c r="X26" s="17"/>
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
-      <c r="AA26" s="18"/>
-      <c r="AB26" s="19"/>
-    </row>
-    <row r="27" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="9"/>
+      <c r="AA26" s="17"/>
+      <c r="AB26" s="18"/>
+    </row>
+    <row r="27" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B27" s="8"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="9"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="8"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="5"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="31"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
@@ -3067,27 +3041,27 @@
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
-      <c r="T27" s="33"/>
-      <c r="U27" s="29"/>
-      <c r="V27" s="9"/>
+      <c r="T27" s="31"/>
+      <c r="U27" s="27"/>
+      <c r="V27" s="8"/>
       <c r="W27" s="2"/>
       <c r="X27" s="2"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="2"/>
-      <c r="AB27" s="17"/>
-    </row>
-    <row r="28" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="9"/>
+      <c r="AB27" s="16"/>
+    </row>
+    <row r="28" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B28" s="8"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="9"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="8"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="5"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="31"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
@@ -3096,27 +3070,27 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
-      <c r="T28" s="33"/>
-      <c r="U28" s="29"/>
-      <c r="V28" s="9"/>
+      <c r="T28" s="31"/>
+      <c r="U28" s="27"/>
+      <c r="V28" s="8"/>
       <c r="W28" s="2"/>
       <c r="X28" s="2"/>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
       <c r="AA28" s="2"/>
-      <c r="AB28" s="17"/>
-    </row>
-    <row r="29" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="9"/>
+      <c r="AB28" s="16"/>
+    </row>
+    <row r="29" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B29" s="8"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="9"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="8"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="5"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="31"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
@@ -3125,27 +3099,27 @@
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
-      <c r="T29" s="33"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="9"/>
+      <c r="T29" s="31"/>
+      <c r="U29" s="27"/>
+      <c r="V29" s="8"/>
       <c r="W29" s="2"/>
       <c r="X29" s="2"/>
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
       <c r="AA29" s="2"/>
-      <c r="AB29" s="17"/>
-    </row>
-    <row r="30" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="9"/>
+      <c r="AB29" s="16"/>
+    </row>
+    <row r="30" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B30" s="8"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="9"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="8"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="5"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="31"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
@@ -3154,27 +3128,27 @@
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
-      <c r="T30" s="33"/>
-      <c r="U30" s="29"/>
-      <c r="V30" s="9"/>
+      <c r="T30" s="31"/>
+      <c r="U30" s="27"/>
+      <c r="V30" s="8"/>
       <c r="W30" s="2"/>
       <c r="X30" s="2"/>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
       <c r="AA30" s="2"/>
-      <c r="AB30" s="17"/>
-    </row>
-    <row r="31" spans="2:28" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B31" s="9"/>
+      <c r="AB30" s="16"/>
+    </row>
+    <row r="31" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B31" s="8"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="9"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="8"/>
       <c r="I31" s="1"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="5"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="31"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
@@ -3183,27 +3157,27 @@
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
-      <c r="T31" s="33"/>
-      <c r="U31" s="29"/>
-      <c r="V31" s="9"/>
+      <c r="T31" s="31"/>
+      <c r="U31" s="27"/>
+      <c r="V31" s="8"/>
       <c r="W31" s="2"/>
       <c r="X31" s="2"/>
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
       <c r="AA31" s="2"/>
-      <c r="AB31" s="17"/>
-    </row>
-    <row r="32" spans="2:28" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="9"/>
+      <c r="AB31" s="16"/>
+    </row>
+    <row r="32" spans="2:28" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B32" s="8"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="9"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="8"/>
       <c r="I32" s="1"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="5"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="31"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
@@ -3212,29 +3186,29 @@
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
-      <c r="T32" s="33"/>
-      <c r="U32" s="29"/>
-      <c r="V32" s="106" t="s">
-        <v>21</v>
-      </c>
-      <c r="W32" s="107"/>
-      <c r="X32" s="107"/>
-      <c r="Y32" s="107"/>
-      <c r="Z32" s="107"/>
-      <c r="AA32" s="107"/>
-      <c r="AB32" s="108"/>
-    </row>
-    <row r="33" spans="2:28" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B33" s="9"/>
+      <c r="T32" s="31"/>
+      <c r="U32" s="27"/>
+      <c r="V32" s="64" t="s">
+        <v>20</v>
+      </c>
+      <c r="W32" s="65"/>
+      <c r="X32" s="65"/>
+      <c r="Y32" s="65"/>
+      <c r="Z32" s="65"/>
+      <c r="AA32" s="65"/>
+      <c r="AB32" s="66"/>
+    </row>
+    <row r="33" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B33" s="8"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="9"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="8"/>
       <c r="I33" s="1"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="5"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="31"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
@@ -3243,37 +3217,37 @@
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
-      <c r="T33" s="33"/>
-      <c r="U33" s="29"/>
-      <c r="V33" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="W33" s="95" t="s">
+      <c r="T33" s="31"/>
+      <c r="U33" s="27"/>
+      <c r="V33" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="W33" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="X33" s="97"/>
-      <c r="Y33" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z33" s="39" t="s">
+      <c r="X33" s="68"/>
+      <c r="Y33" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="AA33" s="95" t="s">
+      <c r="Z33" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="AB33" s="96"/>
-    </row>
-    <row r="34" spans="2:28" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="9"/>
+      <c r="AA33" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB33" s="69"/>
+    </row>
+    <row r="34" spans="2:28" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B34" s="8"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
-      <c r="G34" s="21"/>
-      <c r="H34" s="9"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="8"/>
       <c r="I34" s="1"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="5"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="31"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
@@ -3282,85 +3256,85 @@
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
-      <c r="T34" s="33"/>
-      <c r="U34" s="29"/>
-      <c r="V34" s="9"/>
-      <c r="W34" s="122"/>
-      <c r="X34" s="123"/>
+      <c r="T34" s="31"/>
+      <c r="U34" s="27"/>
+      <c r="V34" s="8"/>
+      <c r="W34" s="58"/>
+      <c r="X34" s="59"/>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
       <c r="AA34" s="1"/>
-      <c r="AB34" s="10"/>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="9"/>
+      <c r="AB34" s="9"/>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B35" s="8"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="23"/>
-      <c r="J35" s="27"/>
-      <c r="K35" s="5"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="32"/>
       <c r="L35" s="1"/>
-      <c r="M35" s="23"/>
-      <c r="N35" s="23"/>
-      <c r="O35" s="23"/>
-      <c r="P35" s="23"/>
-      <c r="Q35" s="23"/>
+      <c r="M35" s="22"/>
+      <c r="N35" s="22"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="22"/>
+      <c r="Q35" s="22"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
-      <c r="T35" s="34"/>
-      <c r="U35" s="37"/>
-      <c r="V35" s="13"/>
-      <c r="W35" s="124"/>
-      <c r="X35" s="125"/>
+      <c r="T35" s="32"/>
+      <c r="U35" s="35"/>
+      <c r="V35" s="12"/>
+      <c r="W35" s="60"/>
+      <c r="X35" s="61"/>
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
       <c r="AA35" s="3"/>
-      <c r="AB35" s="14"/>
-    </row>
-    <row r="36" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="9"/>
+      <c r="AB35" s="13"/>
+    </row>
+    <row r="36" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B36" s="8"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="23"/>
-      <c r="J36" s="27"/>
-      <c r="K36" s="5"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="32"/>
       <c r="L36" s="1"/>
-      <c r="M36" s="23"/>
-      <c r="N36" s="23"/>
-      <c r="O36" s="23"/>
-      <c r="P36" s="23"/>
-      <c r="Q36" s="23"/>
+      <c r="M36" s="22"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="22"/>
+      <c r="P36" s="22"/>
+      <c r="Q36" s="22"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
-      <c r="T36" s="34"/>
-      <c r="U36" s="37"/>
-      <c r="V36" s="13"/>
-      <c r="W36" s="124"/>
-      <c r="X36" s="125"/>
+      <c r="T36" s="32"/>
+      <c r="U36" s="35"/>
+      <c r="V36" s="12"/>
+      <c r="W36" s="60"/>
+      <c r="X36" s="61"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
       <c r="AA36" s="3"/>
-      <c r="AB36" s="14"/>
-    </row>
-    <row r="37" spans="2:28" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B37" s="11"/>
+      <c r="AB36" s="13"/>
+    </row>
+    <row r="37" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B37" s="10"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="11"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="10"/>
       <c r="I37" s="4"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="6"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="30"/>
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
       <c r="N37" s="4"/>
@@ -3369,151 +3343,161 @@
       <c r="Q37" s="4"/>
       <c r="R37" s="4"/>
       <c r="S37" s="4"/>
-      <c r="T37" s="32"/>
-      <c r="U37" s="31"/>
-      <c r="V37" s="11"/>
-      <c r="W37" s="126"/>
-      <c r="X37" s="127"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="29"/>
+      <c r="V37" s="10"/>
+      <c r="W37" s="62"/>
+      <c r="X37" s="63"/>
       <c r="Y37" s="4"/>
       <c r="Z37" s="4"/>
       <c r="AA37" s="4"/>
-      <c r="AB37" s="12"/>
-    </row>
-    <row r="38" spans="2:28" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B38" s="109" t="s">
-        <v>28</v>
-      </c>
-      <c r="C38" s="110"/>
-      <c r="D38" s="110"/>
-      <c r="E38" s="110"/>
-      <c r="F38" s="110"/>
-      <c r="G38" s="110"/>
-      <c r="H38" s="110"/>
-      <c r="I38" s="110"/>
-      <c r="J38" s="110"/>
-      <c r="K38" s="110"/>
-      <c r="L38" s="110"/>
-      <c r="M38" s="110"/>
-      <c r="N38" s="110"/>
-      <c r="O38" s="110"/>
-      <c r="P38" s="110"/>
-      <c r="Q38" s="110"/>
-      <c r="R38" s="110"/>
-      <c r="S38" s="110"/>
-      <c r="T38" s="110"/>
-      <c r="U38" s="40" t="s">
+      <c r="AB37" s="11"/>
+    </row>
+    <row r="38" spans="2:28" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B38" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="V38" s="111" t="s">
-        <v>23</v>
-      </c>
-      <c r="W38" s="111"/>
-      <c r="X38" s="111"/>
-      <c r="Y38" s="111"/>
-      <c r="Z38" s="111"/>
-      <c r="AA38" s="111"/>
-      <c r="AB38" s="112"/>
-    </row>
-    <row r="39" spans="2:28" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="113"/>
-      <c r="C39" s="114"/>
-      <c r="D39" s="114"/>
-      <c r="E39" s="114"/>
-      <c r="F39" s="114"/>
-      <c r="G39" s="114"/>
-      <c r="H39" s="114"/>
-      <c r="I39" s="114"/>
-      <c r="J39" s="114"/>
-      <c r="K39" s="114"/>
-      <c r="L39" s="114"/>
-      <c r="M39" s="114"/>
-      <c r="N39" s="114"/>
-      <c r="O39" s="114"/>
-      <c r="P39" s="114"/>
-      <c r="Q39" s="114"/>
-      <c r="R39" s="114"/>
-      <c r="S39" s="114"/>
-      <c r="T39" s="114"/>
-      <c r="U39" s="119"/>
-      <c r="V39" s="7"/>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="71"/>
+      <c r="L38" s="71"/>
+      <c r="M38" s="71"/>
+      <c r="N38" s="71"/>
+      <c r="O38" s="71"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="71"/>
+      <c r="S38" s="71"/>
+      <c r="T38" s="71"/>
+      <c r="U38" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="V38" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="W38" s="72"/>
+      <c r="X38" s="72"/>
+      <c r="Y38" s="72"/>
+      <c r="Z38" s="72"/>
+      <c r="AA38" s="72"/>
+      <c r="AB38" s="73"/>
+    </row>
+    <row r="39" spans="2:28" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B39" s="49"/>
+      <c r="C39" s="50"/>
+      <c r="D39" s="50"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="50"/>
+      <c r="G39" s="50"/>
+      <c r="H39" s="50"/>
+      <c r="I39" s="50"/>
+      <c r="J39" s="50"/>
+      <c r="K39" s="50"/>
+      <c r="L39" s="50"/>
+      <c r="M39" s="50"/>
+      <c r="N39" s="50"/>
+      <c r="O39" s="50"/>
+      <c r="P39" s="50"/>
+      <c r="Q39" s="50"/>
+      <c r="R39" s="50"/>
+      <c r="S39" s="50"/>
+      <c r="T39" s="50"/>
+      <c r="U39" s="55"/>
+      <c r="V39" s="6"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-      <c r="AB39" s="14"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="115"/>
-      <c r="C40" s="116"/>
-      <c r="D40" s="116"/>
-      <c r="E40" s="116"/>
-      <c r="F40" s="116"/>
-      <c r="G40" s="116"/>
-      <c r="H40" s="116"/>
-      <c r="I40" s="116"/>
-      <c r="J40" s="116"/>
-      <c r="K40" s="116"/>
-      <c r="L40" s="116"/>
-      <c r="M40" s="116"/>
-      <c r="N40" s="116"/>
-      <c r="O40" s="116"/>
-      <c r="P40" s="116"/>
-      <c r="Q40" s="116"/>
-      <c r="R40" s="116"/>
-      <c r="S40" s="116"/>
-      <c r="T40" s="116"/>
-      <c r="U40" s="120"/>
-      <c r="V40" s="7"/>
+      <c r="AB39" s="13"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.45">
+      <c r="B40" s="51"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="52"/>
+      <c r="K40" s="52"/>
+      <c r="L40" s="52"/>
+      <c r="M40" s="52"/>
+      <c r="N40" s="52"/>
+      <c r="O40" s="52"/>
+      <c r="P40" s="52"/>
+      <c r="Q40" s="52"/>
+      <c r="R40" s="52"/>
+      <c r="S40" s="52"/>
+      <c r="T40" s="52"/>
+      <c r="U40" s="56"/>
+      <c r="V40" s="6"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-      <c r="AB40" s="14"/>
-    </row>
-    <row r="41" spans="2:28" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B41" s="117"/>
-      <c r="C41" s="118"/>
-      <c r="D41" s="118"/>
-      <c r="E41" s="118"/>
-      <c r="F41" s="118"/>
-      <c r="G41" s="118"/>
-      <c r="H41" s="118"/>
-      <c r="I41" s="118"/>
-      <c r="J41" s="118"/>
-      <c r="K41" s="118"/>
-      <c r="L41" s="118"/>
-      <c r="M41" s="118"/>
-      <c r="N41" s="118"/>
-      <c r="O41" s="118"/>
-      <c r="P41" s="118"/>
-      <c r="Q41" s="118"/>
-      <c r="R41" s="118"/>
-      <c r="S41" s="118"/>
-      <c r="T41" s="118"/>
-      <c r="U41" s="121"/>
-      <c r="V41" s="22"/>
-      <c r="W41" s="15"/>
-      <c r="X41" s="15"/>
-      <c r="Y41" s="15"/>
-      <c r="Z41" s="15"/>
-      <c r="AA41" s="15"/>
-      <c r="AB41" s="16"/>
+      <c r="AB40" s="13"/>
+    </row>
+    <row r="41" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B41" s="53"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="54"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="54"/>
+      <c r="I41" s="54"/>
+      <c r="J41" s="54"/>
+      <c r="K41" s="54"/>
+      <c r="L41" s="54"/>
+      <c r="M41" s="54"/>
+      <c r="N41" s="54"/>
+      <c r="O41" s="54"/>
+      <c r="P41" s="54"/>
+      <c r="Q41" s="54"/>
+      <c r="R41" s="54"/>
+      <c r="S41" s="54"/>
+      <c r="T41" s="54"/>
+      <c r="U41" s="57"/>
+      <c r="V41" s="21"/>
+      <c r="W41" s="14"/>
+      <c r="X41" s="14"/>
+      <c r="Y41" s="14"/>
+      <c r="Z41" s="14"/>
+      <c r="AA41" s="14"/>
+      <c r="AB41" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="B39:T41"/>
-    <mergeCell ref="U39:U41"/>
-    <mergeCell ref="W34:X34"/>
-    <mergeCell ref="W35:X35"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="W37:X37"/>
-    <mergeCell ref="V32:AB32"/>
-    <mergeCell ref="W33:X33"/>
-    <mergeCell ref="AA33:AB33"/>
-    <mergeCell ref="B38:T38"/>
-    <mergeCell ref="V38:AB38"/>
+  <mergeCells count="41">
+    <mergeCell ref="B2:AB2"/>
+    <mergeCell ref="B3:F5"/>
+    <mergeCell ref="L4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="X4:X5"/>
+    <mergeCell ref="G3:K3"/>
+    <mergeCell ref="G4:K5"/>
+    <mergeCell ref="L3:T3"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="E6:G7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="V4:W5"/>
+    <mergeCell ref="W6:W7"/>
+    <mergeCell ref="V6:V7"/>
     <mergeCell ref="AA25:AB25"/>
     <mergeCell ref="Y3:Z3"/>
     <mergeCell ref="W25:X25"/>
@@ -3523,26 +3507,17 @@
     <mergeCell ref="AA6:AB7"/>
     <mergeCell ref="X6:X7"/>
     <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="V4:W5"/>
-    <mergeCell ref="W6:W7"/>
-    <mergeCell ref="V6:V7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="E6:G7"/>
-    <mergeCell ref="B2:AB2"/>
-    <mergeCell ref="B3:F5"/>
-    <mergeCell ref="L4:T5"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="X4:X5"/>
-    <mergeCell ref="G3:K3"/>
-    <mergeCell ref="G4:K5"/>
-    <mergeCell ref="L3:T3"/>
+    <mergeCell ref="V32:AB32"/>
+    <mergeCell ref="W33:X33"/>
+    <mergeCell ref="AA33:AB33"/>
+    <mergeCell ref="B38:T38"/>
+    <mergeCell ref="V38:AB38"/>
+    <mergeCell ref="B39:T41"/>
+    <mergeCell ref="U39:U41"/>
+    <mergeCell ref="W34:X34"/>
+    <mergeCell ref="W35:X35"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="W37:X37"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/daily_schedule_template.xlsx
+++ b/daily_schedule_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tente\Desktop\避難所HTML\Qbrick_movie_admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD7593B-EA95-4C50-8D36-8657D905CB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CB3A7B-4C2E-49AA-8495-1222545E1062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B38646D7-4FB5-417F-8EB0-63EC9454F196}"/>
   </bookViews>
@@ -1207,7 +1207,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1355,49 +1355,154 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1409,15 +1514,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1430,161 +1526,59 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1821,81 +1815,6 @@
             </a:rPr>
             <a:t>決</a:t>
           </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>317500</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>339396</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>810172</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>1270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="テキスト ボックス 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8787B302-BA6C-6028-E8BC-1F250D305C96}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="974397" y="1992586"/>
-          <a:ext cx="12557672" cy="2550948"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="28575"/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600" b="1"/>
-            <a:t>【</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600" b="1"/>
-            <a:t>撮影メモ</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600" b="1"/>
-            <a:t>】</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600" b="1"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2238,168 +2157,160 @@
   <sheetData>
     <row r="1" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:28" ht="57.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="111" t="s">
+      <c r="B2" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="112"/>
-      <c r="G2" s="112"/>
-      <c r="H2" s="112"/>
-      <c r="I2" s="112"/>
-      <c r="J2" s="112"/>
-      <c r="K2" s="112"/>
-      <c r="L2" s="112"/>
-      <c r="M2" s="112"/>
-      <c r="N2" s="112"/>
-      <c r="O2" s="112"/>
-      <c r="P2" s="112"/>
-      <c r="Q2" s="112"/>
-      <c r="R2" s="112"/>
-      <c r="S2" s="112"/>
-      <c r="T2" s="112"/>
-      <c r="U2" s="112"/>
-      <c r="V2" s="112"/>
-      <c r="W2" s="112"/>
-      <c r="X2" s="112"/>
-      <c r="Y2" s="112"/>
-      <c r="Z2" s="112"/>
-      <c r="AA2" s="112"/>
-      <c r="AB2" s="113"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="53"/>
+      <c r="U2" s="53"/>
+      <c r="V2" s="53"/>
+      <c r="W2" s="53"/>
+      <c r="X2" s="53"/>
+      <c r="Y2" s="53"/>
+      <c r="Z2" s="53"/>
+      <c r="AA2" s="53"/>
+      <c r="AB2" s="54"/>
     </row>
     <row r="3" spans="2:28" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B3" s="114" t="s">
+      <c r="B3" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="92" t="s">
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="92"/>
-      <c r="I3" s="92"/>
-      <c r="J3" s="92"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="123" t="s">
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="123"/>
-      <c r="N3" s="123"/>
-      <c r="O3" s="123"/>
-      <c r="P3" s="123"/>
-      <c r="Q3" s="123"/>
-      <c r="R3" s="123"/>
-      <c r="S3" s="123"/>
-      <c r="T3" s="74"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="67"/>
       <c r="U3" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="V3" s="90" t="s">
+      <c r="V3" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="W3" s="75"/>
+      <c r="W3" s="81"/>
       <c r="X3" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="Y3" s="74" t="s">
+      <c r="Y3" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="Z3" s="75"/>
-      <c r="AA3" s="74" t="s">
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="AB3" s="87"/>
+      <c r="AB3" s="98"/>
     </row>
     <row r="4" spans="2:28" ht="18.45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="116"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118"/>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="118"/>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118"/>
-      <c r="S4" s="118"/>
-      <c r="T4" s="119"/>
-      <c r="U4" s="120"/>
-      <c r="V4" s="91"/>
-      <c r="W4" s="80"/>
-      <c r="X4" s="121"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="80"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+      <c r="L4" s="59"/>
+      <c r="M4" s="59"/>
+      <c r="N4" s="59"/>
+      <c r="O4" s="59"/>
+      <c r="P4" s="59"/>
+      <c r="Q4" s="59"/>
+      <c r="R4" s="59"/>
+      <c r="S4" s="59"/>
+      <c r="T4" s="60"/>
+      <c r="U4" s="61"/>
+      <c r="V4" s="82"/>
+      <c r="W4" s="83"/>
+      <c r="X4" s="62"/>
+      <c r="Y4" s="94"/>
+      <c r="Z4" s="83"/>
       <c r="AA4" s="42" t="s">
         <v>13</v>
       </c>
       <c r="AB4" s="43"/>
     </row>
     <row r="5" spans="2:28" ht="22.2" x14ac:dyDescent="0.45">
-      <c r="B5" s="116"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="118"/>
-      <c r="K5" s="118"/>
-      <c r="L5" s="118"/>
-      <c r="M5" s="118"/>
-      <c r="N5" s="118"/>
-      <c r="O5" s="118"/>
-      <c r="P5" s="118"/>
-      <c r="Q5" s="118"/>
-      <c r="R5" s="118"/>
-      <c r="S5" s="118"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="92"/>
-      <c r="W5" s="82"/>
-      <c r="X5" s="122"/>
-      <c r="Y5" s="81"/>
-      <c r="Z5" s="82"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59"/>
+      <c r="L5" s="59"/>
+      <c r="M5" s="59"/>
+      <c r="N5" s="59"/>
+      <c r="O5" s="59"/>
+      <c r="P5" s="59"/>
+      <c r="Q5" s="59"/>
+      <c r="R5" s="59"/>
+      <c r="S5" s="59"/>
+      <c r="T5" s="60"/>
+      <c r="U5" s="61"/>
+      <c r="V5" s="64"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="63"/>
+      <c r="Y5" s="95"/>
+      <c r="Z5" s="65"/>
       <c r="AA5" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AB5" s="45"/>
     </row>
-    <row r="6" spans="2:28" ht="127.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="97" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="99" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="99" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="105" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="106"/>
-      <c r="G6" s="107"/>
-      <c r="H6" s="95" t="s" ph="1">
+    <row r="6" spans="2:28" ht="127.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="121"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="123"/>
+      <c r="H6" s="68" t="s" ph="1">
         <v>9</v>
       </c>
-      <c r="I6" s="103" t="s">
+      <c r="I6" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="125" t="s">
+      <c r="J6" s="77" t="s">
         <v>31</v>
       </c>
-      <c r="K6" s="101" t="s">
+      <c r="K6" s="70" t="s">
         <v>11</v>
       </c>
       <c r="L6" s="39"/>
@@ -2411,38 +2322,46 @@
       <c r="R6" s="39"/>
       <c r="S6" s="40"/>
       <c r="T6" s="40"/>
-      <c r="U6" s="88" t="s">
+      <c r="U6" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="V6" s="93" t="s">
+      <c r="V6" s="86" t="s">
         <v>25</v>
       </c>
-      <c r="W6" s="83" t="s">
+      <c r="W6" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="X6" s="83" t="s">
+      <c r="X6" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="Y6" s="83" t="s">
+      <c r="Y6" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="Z6" s="83"/>
-      <c r="AA6" s="83" t="s">
+      <c r="Z6" s="84"/>
+      <c r="AA6" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="AB6" s="85"/>
-    </row>
-    <row r="7" spans="2:28" ht="126.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="98"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="109"/>
-      <c r="G7" s="110"/>
-      <c r="H7" s="96" ph="1"/>
-      <c r="I7" s="104"/>
-      <c r="J7" s="104"/>
-      <c r="K7" s="102"/>
+      <c r="AB6" s="96"/>
+    </row>
+    <row r="7" spans="2:28" ht="126.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B7" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="74" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="75"/>
+      <c r="G7" s="76"/>
+      <c r="H7" s="69" ph="1"/>
+      <c r="I7" s="73"/>
+      <c r="J7" s="73"/>
+      <c r="K7" s="71"/>
       <c r="L7" s="46"/>
       <c r="M7" s="47"/>
       <c r="N7" s="47"/>
@@ -2452,14 +2371,14 @@
       <c r="R7" s="46"/>
       <c r="S7" s="46"/>
       <c r="T7" s="48"/>
-      <c r="U7" s="89"/>
-      <c r="V7" s="94"/>
-      <c r="W7" s="84"/>
-      <c r="X7" s="84"/>
-      <c r="Y7" s="84"/>
-      <c r="Z7" s="84"/>
-      <c r="AA7" s="84"/>
-      <c r="AB7" s="86"/>
+      <c r="U7" s="79"/>
+      <c r="V7" s="87"/>
+      <c r="W7" s="85"/>
+      <c r="X7" s="85"/>
+      <c r="Y7" s="85"/>
+      <c r="Z7" s="85"/>
+      <c r="AA7" s="85"/>
+      <c r="AB7" s="97"/>
     </row>
     <row r="8" spans="2:28" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B8" s="12"/>
@@ -2471,7 +2390,7 @@
       <c r="H8" s="12"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
-      <c r="K8" s="124"/>
+      <c r="K8" s="51"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
@@ -2944,15 +2863,15 @@
       <c r="S24" s="1"/>
       <c r="T24" s="31"/>
       <c r="U24" s="34"/>
-      <c r="V24" s="76" t="s">
+      <c r="V24" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="W24" s="77"/>
-      <c r="X24" s="77"/>
-      <c r="Y24" s="77"/>
-      <c r="Z24" s="77"/>
-      <c r="AA24" s="77"/>
-      <c r="AB24" s="78"/>
+      <c r="W24" s="92"/>
+      <c r="X24" s="92"/>
+      <c r="Y24" s="92"/>
+      <c r="Z24" s="92"/>
+      <c r="AA24" s="92"/>
+      <c r="AB24" s="93"/>
     </row>
     <row r="25" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B25" s="8"/>
@@ -2978,20 +2897,20 @@
       <c r="V25" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="W25" s="67" t="s">
+      <c r="W25" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="X25" s="68"/>
+      <c r="X25" s="90"/>
       <c r="Y25" s="37" t="s">
         <v>18</v>
       </c>
       <c r="Z25" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="AA25" s="67" t="s">
+      <c r="AA25" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="AB25" s="69"/>
+      <c r="AB25" s="89"/>
     </row>
     <row r="26" spans="2:28" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B26" s="8"/>
@@ -3188,15 +3107,15 @@
       <c r="S32" s="1"/>
       <c r="T32" s="31"/>
       <c r="U32" s="27"/>
-      <c r="V32" s="64" t="s">
+      <c r="V32" s="99" t="s">
         <v>20</v>
       </c>
-      <c r="W32" s="65"/>
-      <c r="X32" s="65"/>
-      <c r="Y32" s="65"/>
-      <c r="Z32" s="65"/>
-      <c r="AA32" s="65"/>
-      <c r="AB32" s="66"/>
+      <c r="W32" s="100"/>
+      <c r="X32" s="100"/>
+      <c r="Y32" s="100"/>
+      <c r="Z32" s="100"/>
+      <c r="AA32" s="100"/>
+      <c r="AB32" s="101"/>
     </row>
     <row r="33" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B33" s="8"/>
@@ -3222,20 +3141,20 @@
       <c r="V33" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="W33" s="67" t="s">
+      <c r="W33" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="X33" s="68"/>
+      <c r="X33" s="90"/>
       <c r="Y33" s="37" t="s">
         <v>18</v>
       </c>
       <c r="Z33" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="AA33" s="67" t="s">
+      <c r="AA33" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="AB33" s="69"/>
+      <c r="AB33" s="89"/>
     </row>
     <row r="34" spans="2:28" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B34" s="8"/>
@@ -3259,8 +3178,8 @@
       <c r="T34" s="31"/>
       <c r="U34" s="27"/>
       <c r="V34" s="8"/>
-      <c r="W34" s="58"/>
-      <c r="X34" s="59"/>
+      <c r="W34" s="115"/>
+      <c r="X34" s="116"/>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
       <c r="AA34" s="1"/>
@@ -3288,8 +3207,8 @@
       <c r="T35" s="32"/>
       <c r="U35" s="35"/>
       <c r="V35" s="12"/>
-      <c r="W35" s="60"/>
-      <c r="X35" s="61"/>
+      <c r="W35" s="117"/>
+      <c r="X35" s="118"/>
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
       <c r="AA35" s="3"/>
@@ -3317,8 +3236,8 @@
       <c r="T36" s="32"/>
       <c r="U36" s="35"/>
       <c r="V36" s="12"/>
-      <c r="W36" s="60"/>
-      <c r="X36" s="61"/>
+      <c r="W36" s="117"/>
+      <c r="X36" s="118"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
       <c r="AA36" s="3"/>
@@ -3346,69 +3265,69 @@
       <c r="T37" s="30"/>
       <c r="U37" s="29"/>
       <c r="V37" s="10"/>
-      <c r="W37" s="62"/>
-      <c r="X37" s="63"/>
+      <c r="W37" s="119"/>
+      <c r="X37" s="120"/>
       <c r="Y37" s="4"/>
       <c r="Z37" s="4"/>
       <c r="AA37" s="4"/>
       <c r="AB37" s="11"/>
     </row>
     <row r="38" spans="2:28" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B38" s="70" t="s">
+      <c r="B38" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="71"/>
-      <c r="D38" s="71"/>
-      <c r="E38" s="71"/>
-      <c r="F38" s="71"/>
-      <c r="G38" s="71"/>
-      <c r="H38" s="71"/>
-      <c r="I38" s="71"/>
-      <c r="J38" s="71"/>
-      <c r="K38" s="71"/>
-      <c r="L38" s="71"/>
-      <c r="M38" s="71"/>
-      <c r="N38" s="71"/>
-      <c r="O38" s="71"/>
-      <c r="P38" s="71"/>
-      <c r="Q38" s="71"/>
-      <c r="R38" s="71"/>
-      <c r="S38" s="71"/>
-      <c r="T38" s="71"/>
+      <c r="C38" s="103"/>
+      <c r="D38" s="103"/>
+      <c r="E38" s="103"/>
+      <c r="F38" s="103"/>
+      <c r="G38" s="103"/>
+      <c r="H38" s="103"/>
+      <c r="I38" s="103"/>
+      <c r="J38" s="103"/>
+      <c r="K38" s="103"/>
+      <c r="L38" s="103"/>
+      <c r="M38" s="103"/>
+      <c r="N38" s="103"/>
+      <c r="O38" s="103"/>
+      <c r="P38" s="103"/>
+      <c r="Q38" s="103"/>
+      <c r="R38" s="103"/>
+      <c r="S38" s="103"/>
+      <c r="T38" s="103"/>
       <c r="U38" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="V38" s="72" t="s">
+      <c r="V38" s="104" t="s">
         <v>22</v>
       </c>
-      <c r="W38" s="72"/>
-      <c r="X38" s="72"/>
-      <c r="Y38" s="72"/>
-      <c r="Z38" s="72"/>
-      <c r="AA38" s="72"/>
-      <c r="AB38" s="73"/>
+      <c r="W38" s="104"/>
+      <c r="X38" s="104"/>
+      <c r="Y38" s="104"/>
+      <c r="Z38" s="104"/>
+      <c r="AA38" s="104"/>
+      <c r="AB38" s="105"/>
     </row>
     <row r="39" spans="2:28" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B39" s="49"/>
-      <c r="C39" s="50"/>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="50"/>
-      <c r="I39" s="50"/>
-      <c r="J39" s="50"/>
-      <c r="K39" s="50"/>
-      <c r="L39" s="50"/>
-      <c r="M39" s="50"/>
-      <c r="N39" s="50"/>
-      <c r="O39" s="50"/>
-      <c r="P39" s="50"/>
-      <c r="Q39" s="50"/>
-      <c r="R39" s="50"/>
-      <c r="S39" s="50"/>
-      <c r="T39" s="50"/>
-      <c r="U39" s="55"/>
+      <c r="B39" s="106"/>
+      <c r="C39" s="107"/>
+      <c r="D39" s="107"/>
+      <c r="E39" s="107"/>
+      <c r="F39" s="107"/>
+      <c r="G39" s="107"/>
+      <c r="H39" s="107"/>
+      <c r="I39" s="107"/>
+      <c r="J39" s="107"/>
+      <c r="K39" s="107"/>
+      <c r="L39" s="107"/>
+      <c r="M39" s="107"/>
+      <c r="N39" s="107"/>
+      <c r="O39" s="107"/>
+      <c r="P39" s="107"/>
+      <c r="Q39" s="107"/>
+      <c r="R39" s="107"/>
+      <c r="S39" s="107"/>
+      <c r="T39" s="107"/>
+      <c r="U39" s="112"/>
       <c r="V39" s="6"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
@@ -3418,26 +3337,26 @@
       <c r="AB39" s="13"/>
     </row>
     <row r="40" spans="2:28" x14ac:dyDescent="0.45">
-      <c r="B40" s="51"/>
-      <c r="C40" s="52"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="52"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="52"/>
-      <c r="K40" s="52"/>
-      <c r="L40" s="52"/>
-      <c r="M40" s="52"/>
-      <c r="N40" s="52"/>
-      <c r="O40" s="52"/>
-      <c r="P40" s="52"/>
-      <c r="Q40" s="52"/>
-      <c r="R40" s="52"/>
-      <c r="S40" s="52"/>
-      <c r="T40" s="52"/>
-      <c r="U40" s="56"/>
+      <c r="B40" s="108"/>
+      <c r="C40" s="109"/>
+      <c r="D40" s="109"/>
+      <c r="E40" s="109"/>
+      <c r="F40" s="109"/>
+      <c r="G40" s="109"/>
+      <c r="H40" s="109"/>
+      <c r="I40" s="109"/>
+      <c r="J40" s="109"/>
+      <c r="K40" s="109"/>
+      <c r="L40" s="109"/>
+      <c r="M40" s="109"/>
+      <c r="N40" s="109"/>
+      <c r="O40" s="109"/>
+      <c r="P40" s="109"/>
+      <c r="Q40" s="109"/>
+      <c r="R40" s="109"/>
+      <c r="S40" s="109"/>
+      <c r="T40" s="109"/>
+      <c r="U40" s="113"/>
       <c r="V40" s="6"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
@@ -3447,26 +3366,26 @@
       <c r="AB40" s="13"/>
     </row>
     <row r="41" spans="2:28" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B41" s="53"/>
-      <c r="C41" s="54"/>
-      <c r="D41" s="54"/>
-      <c r="E41" s="54"/>
-      <c r="F41" s="54"/>
-      <c r="G41" s="54"/>
-      <c r="H41" s="54"/>
-      <c r="I41" s="54"/>
-      <c r="J41" s="54"/>
-      <c r="K41" s="54"/>
-      <c r="L41" s="54"/>
-      <c r="M41" s="54"/>
-      <c r="N41" s="54"/>
-      <c r="O41" s="54"/>
-      <c r="P41" s="54"/>
-      <c r="Q41" s="54"/>
-      <c r="R41" s="54"/>
-      <c r="S41" s="54"/>
-      <c r="T41" s="54"/>
-      <c r="U41" s="57"/>
+      <c r="B41" s="110"/>
+      <c r="C41" s="111"/>
+      <c r="D41" s="111"/>
+      <c r="E41" s="111"/>
+      <c r="F41" s="111"/>
+      <c r="G41" s="111"/>
+      <c r="H41" s="111"/>
+      <c r="I41" s="111"/>
+      <c r="J41" s="111"/>
+      <c r="K41" s="111"/>
+      <c r="L41" s="111"/>
+      <c r="M41" s="111"/>
+      <c r="N41" s="111"/>
+      <c r="O41" s="111"/>
+      <c r="P41" s="111"/>
+      <c r="Q41" s="111"/>
+      <c r="R41" s="111"/>
+      <c r="S41" s="111"/>
+      <c r="T41" s="111"/>
+      <c r="U41" s="114"/>
       <c r="V41" s="21"/>
       <c r="W41" s="14"/>
       <c r="X41" s="14"/>
@@ -3476,28 +3395,20 @@
       <c r="AB41" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="41">
-    <mergeCell ref="B2:AB2"/>
-    <mergeCell ref="B3:F5"/>
-    <mergeCell ref="L4:T5"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="X4:X5"/>
-    <mergeCell ref="G3:K3"/>
-    <mergeCell ref="G4:K5"/>
-    <mergeCell ref="L3:T3"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="E6:G7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="V4:W5"/>
-    <mergeCell ref="W6:W7"/>
-    <mergeCell ref="V6:V7"/>
+  <mergeCells count="39">
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B39:T41"/>
+    <mergeCell ref="U39:U41"/>
+    <mergeCell ref="W34:X34"/>
+    <mergeCell ref="W35:X35"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="W37:X37"/>
+    <mergeCell ref="V32:AB32"/>
+    <mergeCell ref="W33:X33"/>
+    <mergeCell ref="AA33:AB33"/>
+    <mergeCell ref="B38:T38"/>
+    <mergeCell ref="V38:AB38"/>
     <mergeCell ref="AA25:AB25"/>
     <mergeCell ref="Y3:Z3"/>
     <mergeCell ref="W25:X25"/>
@@ -3507,17 +3418,23 @@
     <mergeCell ref="AA6:AB7"/>
     <mergeCell ref="X6:X7"/>
     <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="V32:AB32"/>
-    <mergeCell ref="W33:X33"/>
-    <mergeCell ref="AA33:AB33"/>
-    <mergeCell ref="B38:T38"/>
-    <mergeCell ref="V38:AB38"/>
-    <mergeCell ref="B39:T41"/>
-    <mergeCell ref="U39:U41"/>
-    <mergeCell ref="W34:X34"/>
-    <mergeCell ref="W35:X35"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="W37:X37"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="V4:W5"/>
+    <mergeCell ref="W6:W7"/>
+    <mergeCell ref="V6:V7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="B2:AB2"/>
+    <mergeCell ref="B3:F5"/>
+    <mergeCell ref="L4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="X4:X5"/>
+    <mergeCell ref="G3:K3"/>
+    <mergeCell ref="G4:K5"/>
+    <mergeCell ref="L3:T3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
